--- a/docs/perechen-otchetov/obrazcy/ФО-06.xlsx
+++ b/docs/perechen-otchetov/obrazcy/ФО-06.xlsx
@@ -630,7 +630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:X75"/>
+  <dimension ref="A1:X78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -934,71 +934,71 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" s="8" t="n"/>
       <c r="E8" s="9" t="n">
-        <v>26516.81649</v>
+        <v>28203.8277</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>22121.7381</v>
+        <v>23339.7381</v>
       </c>
       <c r="G8" s="9" t="n">
-        <v>4344.52838</v>
+        <v>4813.53958</v>
       </c>
       <c r="H8" s="9" t="n">
         <v>50.55001</v>
       </c>
       <c r="I8" s="9" t="n">
-        <v>6903.226</v>
+        <v>8250.82121</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>2106.56596</v>
+        <v>2151.20431</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>2256.92429</v>
+        <v>2301.56264</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>2539.73575</v>
+        <v>3798.05426</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>7299.326</v>
+        <v>7412.87608</v>
       </c>
       <c r="N8" s="9" t="n">
-        <v>2360.88054</v>
+        <v>2399.14198</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>2353.27534</v>
+        <v>2390.30254</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>2585.17012</v>
+        <v>2623.43156</v>
       </c>
       <c r="Q8" s="9" t="n">
-        <v>6052.04475</v>
+        <v>6165.59483</v>
       </c>
       <c r="R8" s="9" t="n">
-        <v>2297.56492</v>
+        <v>2334.59212</v>
       </c>
       <c r="S8" s="9" t="n">
-        <v>1830.37638</v>
+        <v>1868.63782</v>
       </c>
       <c r="T8" s="9" t="n">
-        <v>1924.10345</v>
+        <v>1962.3649</v>
       </c>
       <c r="U8" s="9" t="n">
-        <v>6262.21975</v>
+        <v>6374.53559</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>2095.01178</v>
+        <v>2132.03899</v>
       </c>
       <c r="W8" s="9" t="n">
-        <v>2087.4066</v>
+        <v>2125.66805</v>
       </c>
       <c r="X8" s="9" t="n">
-        <v>2079.80137</v>
+        <v>2116.82858</v>
       </c>
     </row>
     <row r="9" ht="13" customHeight="1">
@@ -1008,71 +1008,71 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" s="12" t="n"/>
       <c r="E9" s="13" t="n">
-        <v>18209.32835</v>
+        <v>19896.33956</v>
       </c>
       <c r="F9" s="13" t="n">
-        <v>15653.5</v>
+        <v>16871.5</v>
       </c>
       <c r="G9" s="13" t="n">
-        <v>2555.82835</v>
+        <v>3024.83955</v>
       </c>
       <c r="H9" s="13" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>5079.02063</v>
+        <v>6426.61584</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>1594.2975</v>
+        <v>1638.93585</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>1745.5225</v>
+        <v>1790.16085</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>1739.20063</v>
+        <v>2997.51914</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>5179.67063</v>
+        <v>5293.22071</v>
       </c>
       <c r="N9" s="13" t="n">
-        <v>1732.87875</v>
+        <v>1771.14019</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>1726.55688</v>
+        <v>1763.58408</v>
       </c>
       <c r="P9" s="13" t="n">
-        <v>1720.235</v>
+        <v>1758.49644</v>
       </c>
       <c r="Q9" s="13" t="n">
-        <v>4208.31021</v>
+        <v>4321.86029</v>
       </c>
       <c r="R9" s="13" t="n">
-        <v>1713.91313</v>
+        <v>1750.94033</v>
       </c>
       <c r="S9" s="13" t="n">
-        <v>1248.00792</v>
+        <v>1286.26936</v>
       </c>
       <c r="T9" s="13" t="n">
-        <v>1246.38917</v>
+        <v>1284.65061</v>
       </c>
       <c r="U9" s="13" t="n">
-        <v>3742.32688</v>
+        <v>3854.64272</v>
       </c>
       <c r="V9" s="13" t="n">
-        <v>1253.76416</v>
+        <v>1290.79136</v>
       </c>
       <c r="W9" s="13" t="n">
-        <v>1247.44231</v>
+        <v>1285.70375</v>
       </c>
       <c r="X9" s="13" t="n">
-        <v>1241.12042</v>
+        <v>1278.14762</v>
       </c>
     </row>
     <row r="10" ht="13" customHeight="1">
@@ -1082,71 +1082,71 @@
         </is>
       </c>
       <c r="B10" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C10" s="15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="16" t="n"/>
       <c r="E10" s="17" t="n">
-        <v>9073.75</v>
+        <v>10760.76121</v>
       </c>
       <c r="F10" s="17" t="n">
-        <v>8010</v>
+        <v>9228</v>
       </c>
       <c r="G10" s="17" t="n">
-        <v>1063.75</v>
+        <v>1532.7612</v>
       </c>
       <c r="H10" s="17" t="n">
         <v>0</v>
       </c>
       <c r="I10" s="17" t="n">
-        <v>2330.3125</v>
+        <v>3677.90771</v>
       </c>
       <c r="J10" s="17" t="n">
-        <v>781.35416</v>
+        <v>825.99251</v>
       </c>
       <c r="K10" s="17" t="n">
-        <v>776.77084</v>
+        <v>821.40919</v>
       </c>
       <c r="L10" s="17" t="n">
-        <v>772.1875</v>
+        <v>2030.50601</v>
       </c>
       <c r="M10" s="17" t="n">
-        <v>2289.0625</v>
+        <v>2402.61258</v>
       </c>
       <c r="N10" s="17" t="n">
-        <v>767.60416</v>
+        <v>805.8656</v>
       </c>
       <c r="O10" s="17" t="n">
-        <v>763.02084</v>
+        <v>800.04804</v>
       </c>
       <c r="P10" s="17" t="n">
-        <v>758.4375</v>
+        <v>796.69894</v>
       </c>
       <c r="Q10" s="17" t="n">
-        <v>2247.8125</v>
+        <v>2361.36258</v>
       </c>
       <c r="R10" s="17" t="n">
-        <v>753.85416</v>
+        <v>790.88136</v>
       </c>
       <c r="S10" s="17" t="n">
-        <v>749.27084</v>
+        <v>787.53228</v>
       </c>
       <c r="T10" s="17" t="n">
-        <v>744.6875</v>
+        <v>782.94894</v>
       </c>
       <c r="U10" s="17" t="n">
-        <v>2206.5625</v>
+        <v>2318.87834</v>
       </c>
       <c r="V10" s="17" t="n">
-        <v>740.10416</v>
+        <v>777.13136</v>
       </c>
       <c r="W10" s="17" t="n">
-        <v>735.52084</v>
+        <v>773.78228</v>
       </c>
       <c r="X10" s="17" t="n">
-        <v>730.9375</v>
+        <v>767.9647</v>
       </c>
     </row>
     <row r="11" ht="13" customHeight="1">
@@ -1364,7 +1364,7 @@
     <row r="14" ht="13" customHeight="1">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>ОсОО «Кут-Мүлк»</t>
+          <t>ОсОО «Ала-Арча Энерго»</t>
         </is>
       </c>
       <c r="B14" s="19" t="n"/>
@@ -1373,782 +1373,782 @@
       </c>
       <c r="D14" s="21" t="n"/>
       <c r="E14" s="22" t="n">
-        <v>5604.375</v>
+        <v>1687.01121</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>5250</v>
+        <v>1218</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>354.375</v>
+        <v>469.0112</v>
       </c>
       <c r="H14" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="22" t="n">
-        <v>1430.625</v>
+        <v>1347.59521</v>
       </c>
       <c r="J14" s="22" t="n">
-        <v>479.0625</v>
+        <v>44.63835</v>
       </c>
       <c r="K14" s="22" t="n">
-        <v>476.875</v>
+        <v>44.63835</v>
       </c>
       <c r="L14" s="22" t="n">
-        <v>474.6875</v>
+        <v>1258.31851</v>
       </c>
       <c r="M14" s="22" t="n">
-        <v>1410.9375</v>
+        <v>113.55008</v>
       </c>
       <c r="N14" s="22" t="n">
-        <v>472.5</v>
+        <v>38.26144</v>
       </c>
       <c r="O14" s="22" t="n">
-        <v>470.3125</v>
+        <v>37.0272</v>
       </c>
       <c r="P14" s="22" t="n">
-        <v>468.125</v>
+        <v>38.26144</v>
       </c>
       <c r="Q14" s="22" t="n">
-        <v>1391.25</v>
+        <v>113.55008</v>
       </c>
       <c r="R14" s="22" t="n">
-        <v>465.9375</v>
+        <v>37.0272</v>
       </c>
       <c r="S14" s="22" t="n">
-        <v>463.75</v>
+        <v>38.26144</v>
       </c>
       <c r="T14" s="22" t="n">
-        <v>461.5625</v>
+        <v>38.26144</v>
       </c>
       <c r="U14" s="22" t="n">
-        <v>1371.5625</v>
+        <v>112.31584</v>
       </c>
       <c r="V14" s="22" t="n">
-        <v>459.375</v>
+        <v>37.0272</v>
       </c>
       <c r="W14" s="22" t="n">
-        <v>457.1875</v>
+        <v>38.26144</v>
       </c>
       <c r="X14" s="22" t="n">
-        <v>455</v>
+        <v>37.0272</v>
       </c>
     </row>
     <row r="15" ht="13" customHeight="1">
       <c r="A15" s="23" t="inlineStr">
         <is>
-          <t>№ 23-1/019 от 05.05.2023, USD</t>
+          <t>№ 21-9/040 от 20.09.2021, EUR</t>
         </is>
       </c>
       <c r="B15" s="24" t="n"/>
       <c r="C15" s="24" t="n"/>
       <c r="D15" s="25" t="n"/>
       <c r="E15" s="26" t="n">
-        <v>5604.375</v>
+        <v>1687.01121</v>
       </c>
       <c r="F15" s="26" t="n">
-        <v>5250</v>
+        <v>1218</v>
       </c>
       <c r="G15" s="26" t="n">
-        <v>354.375</v>
+        <v>469.0112</v>
       </c>
       <c r="H15" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="26" t="n">
-        <v>1430.625</v>
+        <v>1347.59521</v>
       </c>
       <c r="J15" s="26" t="n">
-        <v>479.0625</v>
+        <v>44.63835</v>
       </c>
       <c r="K15" s="26" t="n">
-        <v>476.875</v>
+        <v>44.63835</v>
       </c>
       <c r="L15" s="26" t="n">
-        <v>474.6875</v>
+        <v>1258.31851</v>
       </c>
       <c r="M15" s="26" t="n">
-        <v>1410.9375</v>
+        <v>113.55008</v>
       </c>
       <c r="N15" s="26" t="n">
-        <v>472.5</v>
+        <v>38.26144</v>
       </c>
       <c r="O15" s="26" t="n">
-        <v>470.3125</v>
+        <v>37.0272</v>
       </c>
       <c r="P15" s="26" t="n">
-        <v>468.125</v>
+        <v>38.26144</v>
       </c>
       <c r="Q15" s="26" t="n">
-        <v>1391.25</v>
+        <v>113.55008</v>
       </c>
       <c r="R15" s="26" t="n">
-        <v>465.9375</v>
+        <v>37.0272</v>
       </c>
       <c r="S15" s="26" t="n">
-        <v>463.75</v>
+        <v>38.26144</v>
       </c>
       <c r="T15" s="26" t="n">
-        <v>461.5625</v>
+        <v>38.26144</v>
       </c>
       <c r="U15" s="26" t="n">
-        <v>1371.5625</v>
+        <v>112.31584</v>
       </c>
       <c r="V15" s="26" t="n">
-        <v>459.375</v>
+        <v>37.0272</v>
       </c>
       <c r="W15" s="26" t="n">
-        <v>457.1875</v>
+        <v>38.26144</v>
       </c>
       <c r="X15" s="26" t="n">
-        <v>455</v>
+        <v>37.0272</v>
       </c>
     </row>
     <row r="16" ht="13" customHeight="1">
       <c r="A16" s="27" t="inlineStr">
         <is>
-          <t>в тыс. USD (курс 87,50000)</t>
+          <t>в тыс. EUR (курс 101,50000)</t>
         </is>
       </c>
       <c r="B16" s="28" t="n"/>
       <c r="C16" s="28" t="n"/>
       <c r="D16" s="29" t="n"/>
       <c r="E16" s="30" t="n">
+        <v>16.62081</v>
+      </c>
+      <c r="F16" s="30" t="n">
+        <v>12</v>
+      </c>
+      <c r="G16" s="30" t="n">
+        <v>4.6208</v>
+      </c>
+      <c r="H16" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="30" t="n">
+        <v>13.27681</v>
+      </c>
+      <c r="J16" s="30" t="n">
+        <v>0.43979</v>
+      </c>
+      <c r="K16" s="30" t="n">
+        <v>0.43979</v>
+      </c>
+      <c r="L16" s="30" t="n">
+        <v>12.39723</v>
+      </c>
+      <c r="M16" s="30" t="n">
+        <v>1.11872</v>
+      </c>
+      <c r="N16" s="30" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="O16" s="30" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="P16" s="30" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="Q16" s="30" t="n">
+        <v>1.11872</v>
+      </c>
+      <c r="R16" s="30" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="S16" s="30" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="T16" s="30" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="U16" s="30" t="n">
+        <v>1.10656</v>
+      </c>
+      <c r="V16" s="30" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="W16" s="30" t="n">
+        <v>0.37696</v>
+      </c>
+      <c r="X16" s="30" t="n">
+        <v>0.3648</v>
+      </c>
+    </row>
+    <row r="17" ht="13" customHeight="1">
+      <c r="A17" s="18" t="inlineStr">
+        <is>
+          <t>ОсОО «Кут-Мүлк»</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="n"/>
+      <c r="C17" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" s="21" t="n"/>
+      <c r="E17" s="22" t="n">
+        <v>5604.375</v>
+      </c>
+      <c r="F17" s="22" t="n">
+        <v>5250</v>
+      </c>
+      <c r="G17" s="22" t="n">
+        <v>354.375</v>
+      </c>
+      <c r="H17" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="22" t="n">
+        <v>1430.625</v>
+      </c>
+      <c r="J17" s="22" t="n">
+        <v>479.0625</v>
+      </c>
+      <c r="K17" s="22" t="n">
+        <v>476.875</v>
+      </c>
+      <c r="L17" s="22" t="n">
+        <v>474.6875</v>
+      </c>
+      <c r="M17" s="22" t="n">
+        <v>1410.9375</v>
+      </c>
+      <c r="N17" s="22" t="n">
+        <v>472.5</v>
+      </c>
+      <c r="O17" s="22" t="n">
+        <v>470.3125</v>
+      </c>
+      <c r="P17" s="22" t="n">
+        <v>468.125</v>
+      </c>
+      <c r="Q17" s="22" t="n">
+        <v>1391.25</v>
+      </c>
+      <c r="R17" s="22" t="n">
+        <v>465.9375</v>
+      </c>
+      <c r="S17" s="22" t="n">
+        <v>463.75</v>
+      </c>
+      <c r="T17" s="22" t="n">
+        <v>461.5625</v>
+      </c>
+      <c r="U17" s="22" t="n">
+        <v>1371.5625</v>
+      </c>
+      <c r="V17" s="22" t="n">
+        <v>459.375</v>
+      </c>
+      <c r="W17" s="22" t="n">
+        <v>457.1875</v>
+      </c>
+      <c r="X17" s="22" t="n">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="18" ht="13" customHeight="1">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>№ 23-1/019 от 05.05.2023, USD</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="n"/>
+      <c r="C18" s="24" t="n"/>
+      <c r="D18" s="25" t="n"/>
+      <c r="E18" s="26" t="n">
+        <v>5604.375</v>
+      </c>
+      <c r="F18" s="26" t="n">
+        <v>5250</v>
+      </c>
+      <c r="G18" s="26" t="n">
+        <v>354.375</v>
+      </c>
+      <c r="H18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="26" t="n">
+        <v>1430.625</v>
+      </c>
+      <c r="J18" s="26" t="n">
+        <v>479.0625</v>
+      </c>
+      <c r="K18" s="26" t="n">
+        <v>476.875</v>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>474.6875</v>
+      </c>
+      <c r="M18" s="26" t="n">
+        <v>1410.9375</v>
+      </c>
+      <c r="N18" s="26" t="n">
+        <v>472.5</v>
+      </c>
+      <c r="O18" s="26" t="n">
+        <v>470.3125</v>
+      </c>
+      <c r="P18" s="26" t="n">
+        <v>468.125</v>
+      </c>
+      <c r="Q18" s="26" t="n">
+        <v>1391.25</v>
+      </c>
+      <c r="R18" s="26" t="n">
+        <v>465.9375</v>
+      </c>
+      <c r="S18" s="26" t="n">
+        <v>463.75</v>
+      </c>
+      <c r="T18" s="26" t="n">
+        <v>461.5625</v>
+      </c>
+      <c r="U18" s="26" t="n">
+        <v>1371.5625</v>
+      </c>
+      <c r="V18" s="26" t="n">
+        <v>459.375</v>
+      </c>
+      <c r="W18" s="26" t="n">
+        <v>457.1875</v>
+      </c>
+      <c r="X18" s="26" t="n">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="19" ht="13" customHeight="1">
+      <c r="A19" s="27" t="inlineStr">
+        <is>
+          <t>в тыс. USD (курс 87,50000)</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="n"/>
+      <c r="C19" s="28" t="n"/>
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="30" t="n">
         <v>64.05</v>
       </c>
-      <c r="F16" s="30" t="n">
+      <c r="F19" s="30" t="n">
         <v>60</v>
       </c>
-      <c r="G16" s="30" t="n">
+      <c r="G19" s="30" t="n">
         <v>4.05</v>
       </c>
-      <c r="H16" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="30" t="n">
+      <c r="H19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="30" t="n">
         <v>16.35</v>
       </c>
-      <c r="J16" s="30" t="n">
+      <c r="J19" s="30" t="n">
         <v>5.475</v>
       </c>
-      <c r="K16" s="30" t="n">
+      <c r="K19" s="30" t="n">
         <v>5.45</v>
       </c>
-      <c r="L16" s="30" t="n">
+      <c r="L19" s="30" t="n">
         <v>5.425</v>
       </c>
-      <c r="M16" s="30" t="n">
+      <c r="M19" s="30" t="n">
         <v>16.125</v>
       </c>
-      <c r="N16" s="30" t="n">
+      <c r="N19" s="30" t="n">
         <v>5.4</v>
       </c>
-      <c r="O16" s="30" t="n">
+      <c r="O19" s="30" t="n">
         <v>5.375</v>
       </c>
-      <c r="P16" s="30" t="n">
+      <c r="P19" s="30" t="n">
         <v>5.35</v>
       </c>
-      <c r="Q16" s="30" t="n">
+      <c r="Q19" s="30" t="n">
         <v>15.9</v>
       </c>
-      <c r="R16" s="30" t="n">
+      <c r="R19" s="30" t="n">
         <v>5.325</v>
       </c>
-      <c r="S16" s="30" t="n">
+      <c r="S19" s="30" t="n">
         <v>5.3</v>
       </c>
-      <c r="T16" s="30" t="n">
+      <c r="T19" s="30" t="n">
         <v>5.275</v>
       </c>
-      <c r="U16" s="30" t="n">
+      <c r="U19" s="30" t="n">
         <v>15.675</v>
       </c>
-      <c r="V16" s="30" t="n">
+      <c r="V19" s="30" t="n">
         <v>5.25</v>
       </c>
-      <c r="W16" s="30" t="n">
+      <c r="W19" s="30" t="n">
         <v>5.225</v>
       </c>
-      <c r="X16" s="30" t="n">
+      <c r="X19" s="30" t="n">
         <v>5.2</v>
       </c>
     </row>
-    <row r="17" ht="13" customHeight="1">
-      <c r="A17" s="14" t="inlineStr">
+    <row r="20" ht="13" customHeight="1">
+      <c r="A20" s="14" t="inlineStr">
         <is>
           <t>Группа 1.2 — с отставанием от графика</t>
         </is>
       </c>
-      <c r="B17" s="15" t="n">
+      <c r="B20" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="C17" s="15" t="n">
+      <c r="C20" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="17" t="n">
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="17" t="n">
         <v>5918.49502</v>
       </c>
-      <c r="F17" s="17" t="n">
+      <c r="F20" s="17" t="n">
         <v>5193.5</v>
       </c>
-      <c r="G17" s="17" t="n">
+      <c r="G20" s="17" t="n">
         <v>724.99502</v>
       </c>
-      <c r="H17" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="17" t="n">
+      <c r="H20" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="17" t="n">
         <v>1369.95813</v>
       </c>
-      <c r="J17" s="17" t="n">
+      <c r="J20" s="17" t="n">
         <v>353.36001</v>
       </c>
-      <c r="K17" s="17" t="n">
+      <c r="K20" s="17" t="n">
         <v>509.16833</v>
       </c>
-      <c r="L17" s="17" t="n">
+      <c r="L20" s="17" t="n">
         <v>507.4298</v>
       </c>
-      <c r="M17" s="17" t="n">
+      <c r="M20" s="17" t="n">
         <v>1511.85813</v>
       </c>
-      <c r="N17" s="17" t="n">
+      <c r="N20" s="17" t="n">
         <v>505.69126</v>
       </c>
-      <c r="O17" s="17" t="n">
+      <c r="O20" s="17" t="n">
         <v>503.95271</v>
       </c>
-      <c r="P17" s="17" t="n">
+      <c r="P20" s="17" t="n">
         <v>502.21417</v>
       </c>
-      <c r="Q17" s="17" t="n">
+      <c r="Q20" s="17" t="n">
         <v>1500.91438</v>
       </c>
-      <c r="R17" s="17" t="n">
+      <c r="R20" s="17" t="n">
         <v>500.47564</v>
       </c>
-      <c r="S17" s="17" t="n">
+      <c r="S20" s="17" t="n">
         <v>498.73708</v>
       </c>
-      <c r="T17" s="17" t="n">
+      <c r="T20" s="17" t="n">
         <v>501.70167</v>
       </c>
-      <c r="U17" s="17" t="n">
+      <c r="U20" s="17" t="n">
         <v>1535.76438</v>
       </c>
-      <c r="V17" s="17" t="n">
+      <c r="V20" s="17" t="n">
         <v>513.66</v>
       </c>
-      <c r="W17" s="17" t="n">
+      <c r="W20" s="17" t="n">
         <v>511.92147</v>
       </c>
-      <c r="X17" s="17" t="n">
+      <c r="X20" s="17" t="n">
         <v>510.18292</v>
       </c>
     </row>
-    <row r="18" ht="13" customHeight="1">
-      <c r="A18" s="18" t="inlineStr">
+    <row r="21" ht="13" customHeight="1">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>КФХ «Жайыл»</t>
         </is>
       </c>
-      <c r="B18" s="19" t="n"/>
-      <c r="C18" s="20" t="n">
+      <c r="B21" s="19" t="n"/>
+      <c r="C21" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D18" s="21" t="n"/>
-      <c r="E18" s="22" t="n">
+      <c r="D21" s="21" t="n"/>
+      <c r="E21" s="22" t="n">
         <v>232.1</v>
       </c>
-      <c r="F18" s="22" t="n">
+      <c r="F21" s="22" t="n">
         <v>198</v>
       </c>
-      <c r="G18" s="22" t="n">
+      <c r="G21" s="22" t="n">
         <v>34.1</v>
       </c>
-      <c r="H18" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="22" t="n">
+      <c r="H21" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="22" t="n">
         <v>43.55</v>
       </c>
-      <c r="J18" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="22" t="n">
+      <c r="J21" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="22" t="n">
         <v>21.85</v>
       </c>
-      <c r="L18" s="22" t="n">
+      <c r="L21" s="22" t="n">
         <v>21.7</v>
       </c>
-      <c r="M18" s="22" t="n">
+      <c r="M21" s="22" t="n">
         <v>64.2</v>
       </c>
-      <c r="N18" s="22" t="n">
+      <c r="N21" s="22" t="n">
         <v>21.55</v>
       </c>
-      <c r="O18" s="22" t="n">
+      <c r="O21" s="22" t="n">
         <v>21.4</v>
       </c>
-      <c r="P18" s="22" t="n">
+      <c r="P21" s="22" t="n">
         <v>21.25</v>
       </c>
-      <c r="Q18" s="22" t="n">
+      <c r="Q21" s="22" t="n">
         <v>62.85</v>
       </c>
-      <c r="R18" s="22" t="n">
+      <c r="R21" s="22" t="n">
         <v>21.1</v>
       </c>
-      <c r="S18" s="22" t="n">
+      <c r="S21" s="22" t="n">
         <v>20.95</v>
       </c>
-      <c r="T18" s="22" t="n">
+      <c r="T21" s="22" t="n">
         <v>20.8</v>
       </c>
-      <c r="U18" s="22" t="n">
+      <c r="U21" s="22" t="n">
         <v>61.5</v>
       </c>
-      <c r="V18" s="22" t="n">
+      <c r="V21" s="22" t="n">
         <v>20.65</v>
       </c>
-      <c r="W18" s="22" t="n">
+      <c r="W21" s="22" t="n">
         <v>20.5</v>
       </c>
-      <c r="X18" s="22" t="n">
+      <c r="X21" s="22" t="n">
         <v>20.35</v>
       </c>
     </row>
-    <row r="19" ht="13" customHeight="1">
-      <c r="A19" s="23" t="inlineStr">
+    <row r="22" ht="13" customHeight="1">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t>№ 23-4/008 от 20.06.2023, KGS</t>
         </is>
       </c>
-      <c r="B19" s="24" t="n"/>
-      <c r="C19" s="24" t="n"/>
-      <c r="D19" s="25" t="n"/>
-      <c r="E19" s="26" t="n">
+      <c r="B22" s="24" t="n"/>
+      <c r="C22" s="24" t="n"/>
+      <c r="D22" s="25" t="n"/>
+      <c r="E22" s="26" t="n">
         <v>232.1</v>
       </c>
-      <c r="F19" s="26" t="n">
+      <c r="F22" s="26" t="n">
         <v>198</v>
       </c>
-      <c r="G19" s="26" t="n">
+      <c r="G22" s="26" t="n">
         <v>34.1</v>
       </c>
-      <c r="H19" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="26" t="n">
+      <c r="H22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="26" t="n">
         <v>43.55</v>
       </c>
-      <c r="J19" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="26" t="n">
+      <c r="J22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="26" t="n">
         <v>21.85</v>
       </c>
-      <c r="L19" s="26" t="n">
+      <c r="L22" s="26" t="n">
         <v>21.7</v>
       </c>
-      <c r="M19" s="26" t="n">
+      <c r="M22" s="26" t="n">
         <v>64.2</v>
       </c>
-      <c r="N19" s="26" t="n">
+      <c r="N22" s="26" t="n">
         <v>21.55</v>
       </c>
-      <c r="O19" s="26" t="n">
+      <c r="O22" s="26" t="n">
         <v>21.4</v>
       </c>
-      <c r="P19" s="26" t="n">
+      <c r="P22" s="26" t="n">
         <v>21.25</v>
       </c>
-      <c r="Q19" s="26" t="n">
+      <c r="Q22" s="26" t="n">
         <v>62.85</v>
       </c>
-      <c r="R19" s="26" t="n">
+      <c r="R22" s="26" t="n">
         <v>21.1</v>
       </c>
-      <c r="S19" s="26" t="n">
+      <c r="S22" s="26" t="n">
         <v>20.95</v>
       </c>
-      <c r="T19" s="26" t="n">
+      <c r="T22" s="26" t="n">
         <v>20.8</v>
       </c>
-      <c r="U19" s="26" t="n">
+      <c r="U22" s="26" t="n">
         <v>61.5</v>
       </c>
-      <c r="V19" s="26" t="n">
+      <c r="V22" s="26" t="n">
         <v>20.65</v>
       </c>
-      <c r="W19" s="26" t="n">
+      <c r="W22" s="26" t="n">
         <v>20.5</v>
       </c>
-      <c r="X19" s="26" t="n">
+      <c r="X22" s="26" t="n">
         <v>20.35</v>
       </c>
     </row>
-    <row r="20" ht="13" customHeight="1">
-      <c r="A20" s="18" t="inlineStr">
+    <row r="23" ht="13" customHeight="1">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>ОсОО «Кара-Балта Мел»</t>
         </is>
       </c>
-      <c r="B20" s="19" t="n"/>
-      <c r="C20" s="20" t="n">
+      <c r="B23" s="19" t="n"/>
+      <c r="C23" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D20" s="21" t="n"/>
-      <c r="E20" s="22" t="n">
+      <c r="D23" s="21" t="n"/>
+      <c r="E23" s="22" t="n">
         <v>724.7</v>
       </c>
-      <c r="F20" s="22" t="n">
+      <c r="F23" s="22" t="n">
         <v>510</v>
       </c>
-      <c r="G20" s="22" t="n">
+      <c r="G23" s="22" t="n">
         <v>214.7</v>
       </c>
-      <c r="H20" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="22" t="n">
+      <c r="H23" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="22" t="n">
         <v>173.75</v>
       </c>
-      <c r="J20" s="22" t="n">
+      <c r="J23" s="22" t="n">
         <v>58.33334</v>
       </c>
-      <c r="K20" s="22" t="n">
+      <c r="K23" s="22" t="n">
         <v>57.91666</v>
       </c>
-      <c r="L20" s="22" t="n">
+      <c r="L23" s="22" t="n">
         <v>57.5</v>
       </c>
-      <c r="M20" s="22" t="n">
+      <c r="M23" s="22" t="n">
         <v>170</v>
       </c>
-      <c r="N20" s="22" t="n">
+      <c r="N23" s="22" t="n">
         <v>57.08334</v>
       </c>
-      <c r="O20" s="22" t="n">
+      <c r="O23" s="22" t="n">
         <v>56.66666</v>
       </c>
-      <c r="P20" s="22" t="n">
+      <c r="P23" s="22" t="n">
         <v>56.25</v>
       </c>
-      <c r="Q20" s="22" t="n">
+      <c r="Q23" s="22" t="n">
         <v>163.25</v>
       </c>
-      <c r="R20" s="22" t="n">
+      <c r="R23" s="22" t="n">
         <v>55.83334</v>
       </c>
-      <c r="S20" s="22" t="n">
+      <c r="S23" s="22" t="n">
         <v>55.41666</v>
       </c>
-      <c r="T20" s="22" t="n">
+      <c r="T23" s="22" t="n">
         <v>52</v>
       </c>
-      <c r="U20" s="22" t="n">
+      <c r="U23" s="22" t="n">
         <v>217.7</v>
       </c>
-      <c r="V20" s="22" t="n">
+      <c r="V23" s="22" t="n">
         <v>72.98333</v>
       </c>
-      <c r="W20" s="22" t="n">
+      <c r="W23" s="22" t="n">
         <v>72.56667</v>
       </c>
-      <c r="X20" s="22" t="n">
+      <c r="X23" s="22" t="n">
         <v>72.15000000000001</v>
       </c>
     </row>
-    <row r="21" ht="13" customHeight="1">
-      <c r="A21" s="23" t="inlineStr">
+    <row r="24" ht="13" customHeight="1">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>№ 20-2/090 от 12.08.2020, KGS</t>
         </is>
       </c>
-      <c r="B21" s="24" t="n"/>
-      <c r="C21" s="24" t="n"/>
-      <c r="D21" s="31" t="n">
+      <c r="B24" s="24" t="n"/>
+      <c r="C24" s="24" t="n"/>
+      <c r="D24" s="31" t="n">
         <v>46275</v>
       </c>
-      <c r="E21" s="26" t="n">
+      <c r="E24" s="26" t="n">
         <v>724.7</v>
       </c>
-      <c r="F21" s="26" t="n">
+      <c r="F24" s="26" t="n">
         <v>510</v>
       </c>
-      <c r="G21" s="26" t="n">
+      <c r="G24" s="26" t="n">
         <v>214.7</v>
       </c>
-      <c r="H21" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="26" t="n">
+      <c r="H24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="26" t="n">
         <v>173.75</v>
       </c>
-      <c r="J21" s="26" t="n">
+      <c r="J24" s="26" t="n">
         <v>58.33334</v>
       </c>
-      <c r="K21" s="26" t="n">
+      <c r="K24" s="26" t="n">
         <v>57.91666</v>
       </c>
-      <c r="L21" s="26" t="n">
+      <c r="L24" s="26" t="n">
         <v>57.5</v>
       </c>
-      <c r="M21" s="26" t="n">
+      <c r="M24" s="26" t="n">
         <v>170</v>
       </c>
-      <c r="N21" s="26" t="n">
+      <c r="N24" s="26" t="n">
         <v>57.08334</v>
       </c>
-      <c r="O21" s="26" t="n">
+      <c r="O24" s="26" t="n">
         <v>56.66666</v>
       </c>
-      <c r="P21" s="26" t="n">
+      <c r="P24" s="26" t="n">
         <v>56.25</v>
       </c>
-      <c r="Q21" s="26" t="n">
+      <c r="Q24" s="26" t="n">
         <v>163.25</v>
       </c>
-      <c r="R21" s="26" t="n">
+      <c r="R24" s="26" t="n">
         <v>55.83334</v>
       </c>
-      <c r="S21" s="26" t="n">
+      <c r="S24" s="26" t="n">
         <v>55.41666</v>
       </c>
-      <c r="T21" s="26" t="n">
+      <c r="T24" s="26" t="n">
         <v>52</v>
       </c>
-      <c r="U21" s="26" t="n">
+      <c r="U24" s="26" t="n">
         <v>217.7</v>
       </c>
-      <c r="V21" s="26" t="n">
+      <c r="V24" s="26" t="n">
         <v>72.98333</v>
       </c>
-      <c r="W21" s="26" t="n">
+      <c r="W24" s="26" t="n">
         <v>72.56667</v>
       </c>
-      <c r="X21" s="26" t="n">
+      <c r="X24" s="26" t="n">
         <v>72.15000000000001</v>
-      </c>
-    </row>
-    <row r="22" ht="13" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
-        <is>
-          <t>ОсОО «Сулайман-Тоо Трейд»</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="n"/>
-      <c r="C22" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" s="21" t="n"/>
-      <c r="E22" s="22" t="n">
-        <v>3540.32</v>
-      </c>
-      <c r="F22" s="22" t="n">
-        <v>3248</v>
-      </c>
-      <c r="G22" s="22" t="n">
-        <v>292.32</v>
-      </c>
-      <c r="H22" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="22" t="n">
-        <v>885.08</v>
-      </c>
-      <c r="J22" s="22" t="n">
-        <v>295.02667</v>
-      </c>
-      <c r="K22" s="22" t="n">
-        <v>295.02667</v>
-      </c>
-      <c r="L22" s="22" t="n">
-        <v>295.02667</v>
-      </c>
-      <c r="M22" s="22" t="n">
-        <v>885.08</v>
-      </c>
-      <c r="N22" s="22" t="n">
-        <v>295.02667</v>
-      </c>
-      <c r="O22" s="22" t="n">
-        <v>295.02667</v>
-      </c>
-      <c r="P22" s="22" t="n">
-        <v>295.02667</v>
-      </c>
-      <c r="Q22" s="22" t="n">
-        <v>885.08</v>
-      </c>
-      <c r="R22" s="22" t="n">
-        <v>295.02667</v>
-      </c>
-      <c r="S22" s="22" t="n">
-        <v>295.02667</v>
-      </c>
-      <c r="T22" s="22" t="n">
-        <v>295.02667</v>
-      </c>
-      <c r="U22" s="22" t="n">
-        <v>885.08</v>
-      </c>
-      <c r="V22" s="22" t="n">
-        <v>295.02667</v>
-      </c>
-      <c r="W22" s="22" t="n">
-        <v>295.02667</v>
-      </c>
-      <c r="X22" s="22" t="n">
-        <v>295.02667</v>
-      </c>
-    </row>
-    <row r="23" ht="13" customHeight="1">
-      <c r="A23" s="23" t="inlineStr">
-        <is>
-          <t>№ 21-1/207 от 15.11.2021, EUR</t>
-        </is>
-      </c>
-      <c r="B23" s="24" t="n"/>
-      <c r="C23" s="24" t="n"/>
-      <c r="D23" s="25" t="n"/>
-      <c r="E23" s="26" t="n">
-        <v>3540.32</v>
-      </c>
-      <c r="F23" s="26" t="n">
-        <v>3248</v>
-      </c>
-      <c r="G23" s="26" t="n">
-        <v>292.32</v>
-      </c>
-      <c r="H23" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="26" t="n">
-        <v>885.08</v>
-      </c>
-      <c r="J23" s="26" t="n">
-        <v>295.02667</v>
-      </c>
-      <c r="K23" s="26" t="n">
-        <v>295.02667</v>
-      </c>
-      <c r="L23" s="26" t="n">
-        <v>295.02667</v>
-      </c>
-      <c r="M23" s="26" t="n">
-        <v>885.08</v>
-      </c>
-      <c r="N23" s="26" t="n">
-        <v>295.02667</v>
-      </c>
-      <c r="O23" s="26" t="n">
-        <v>295.02667</v>
-      </c>
-      <c r="P23" s="26" t="n">
-        <v>295.02667</v>
-      </c>
-      <c r="Q23" s="26" t="n">
-        <v>885.08</v>
-      </c>
-      <c r="R23" s="26" t="n">
-        <v>295.02667</v>
-      </c>
-      <c r="S23" s="26" t="n">
-        <v>295.02667</v>
-      </c>
-      <c r="T23" s="26" t="n">
-        <v>295.02667</v>
-      </c>
-      <c r="U23" s="26" t="n">
-        <v>885.08</v>
-      </c>
-      <c r="V23" s="26" t="n">
-        <v>295.02667</v>
-      </c>
-      <c r="W23" s="26" t="n">
-        <v>295.02667</v>
-      </c>
-      <c r="X23" s="26" t="n">
-        <v>295.02667</v>
-      </c>
-    </row>
-    <row r="24" ht="13" customHeight="1">
-      <c r="A24" s="27" t="inlineStr">
-        <is>
-          <t>в тыс. EUR (курс 101,50000)</t>
-        </is>
-      </c>
-      <c r="B24" s="28" t="n"/>
-      <c r="C24" s="28" t="n"/>
-      <c r="D24" s="29" t="n"/>
-      <c r="E24" s="30" t="n">
-        <v>34.88</v>
-      </c>
-      <c r="F24" s="30" t="n">
-        <v>32</v>
-      </c>
-      <c r="G24" s="30" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="H24" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="30" t="n">
-        <v>8.720000000000001</v>
-      </c>
-      <c r="J24" s="30" t="n">
-        <v>2.90667</v>
-      </c>
-      <c r="K24" s="30" t="n">
-        <v>2.90667</v>
-      </c>
-      <c r="L24" s="30" t="n">
-        <v>2.90667</v>
-      </c>
-      <c r="M24" s="30" t="n">
-        <v>8.720000000000001</v>
-      </c>
-      <c r="N24" s="30" t="n">
-        <v>2.90667</v>
-      </c>
-      <c r="O24" s="30" t="n">
-        <v>2.90667</v>
-      </c>
-      <c r="P24" s="30" t="n">
-        <v>2.90667</v>
-      </c>
-      <c r="Q24" s="30" t="n">
-        <v>8.720000000000001</v>
-      </c>
-      <c r="R24" s="30" t="n">
-        <v>2.90667</v>
-      </c>
-      <c r="S24" s="30" t="n">
-        <v>2.90667</v>
-      </c>
-      <c r="T24" s="30" t="n">
-        <v>2.90667</v>
-      </c>
-      <c r="U24" s="30" t="n">
-        <v>8.720000000000001</v>
-      </c>
-      <c r="V24" s="30" t="n">
-        <v>2.90667</v>
-      </c>
-      <c r="W24" s="30" t="n">
-        <v>2.90667</v>
-      </c>
-      <c r="X24" s="30" t="n">
-        <v>2.90667</v>
       </c>
     </row>
     <row r="25" ht="13" customHeight="1">
       <c r="A25" s="18" t="inlineStr">
         <is>
-          <t>ОсОО «Тянь-Шань Строй»</t>
+          <t>ОсОО «Сулайман-Тоо Трейд»</t>
         </is>
       </c>
       <c r="B25" s="19" t="n"/>
@@ -2157,500 +2157,498 @@
       </c>
       <c r="D25" s="21" t="n"/>
       <c r="E25" s="22" t="n">
-        <v>1421.37502</v>
+        <v>3540.32</v>
       </c>
       <c r="F25" s="22" t="n">
-        <v>1237.5</v>
+        <v>3248</v>
       </c>
       <c r="G25" s="22" t="n">
-        <v>183.87502</v>
+        <v>292.32</v>
       </c>
       <c r="H25" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I25" s="22" t="n">
-        <v>267.57813</v>
+        <v>885.08</v>
       </c>
       <c r="J25" s="22" t="n">
-        <v>0</v>
+        <v>295.02667</v>
       </c>
       <c r="K25" s="22" t="n">
-        <v>134.375</v>
+        <v>295.02667</v>
       </c>
       <c r="L25" s="22" t="n">
-        <v>133.20313</v>
+        <v>295.02667</v>
       </c>
       <c r="M25" s="22" t="n">
-        <v>392.57813</v>
+        <v>885.08</v>
       </c>
       <c r="N25" s="22" t="n">
-        <v>132.03125</v>
+        <v>295.02667</v>
       </c>
       <c r="O25" s="22" t="n">
-        <v>130.85938</v>
+        <v>295.02667</v>
       </c>
       <c r="P25" s="22" t="n">
-        <v>129.6875</v>
+        <v>295.02667</v>
       </c>
       <c r="Q25" s="22" t="n">
-        <v>389.73438</v>
+        <v>885.08</v>
       </c>
       <c r="R25" s="22" t="n">
-        <v>128.51563</v>
+        <v>295.02667</v>
       </c>
       <c r="S25" s="22" t="n">
-        <v>127.34375</v>
+        <v>295.02667</v>
       </c>
       <c r="T25" s="22" t="n">
-        <v>133.875</v>
+        <v>295.02667</v>
       </c>
       <c r="U25" s="22" t="n">
-        <v>371.48438</v>
+        <v>885.08</v>
       </c>
       <c r="V25" s="22" t="n">
-        <v>125</v>
+        <v>295.02667</v>
       </c>
       <c r="W25" s="22" t="n">
-        <v>123.82813</v>
+        <v>295.02667</v>
       </c>
       <c r="X25" s="22" t="n">
-        <v>122.65625</v>
+        <v>295.02667</v>
       </c>
     </row>
     <row r="26" ht="13" customHeight="1">
       <c r="A26" s="23" t="inlineStr">
         <is>
-          <t>№ 22-1/045 от 03.02.2022, KGS</t>
+          <t>№ 21-1/207 от 15.11.2021, EUR</t>
         </is>
       </c>
       <c r="B26" s="24" t="n"/>
       <c r="C26" s="24" t="n"/>
       <c r="D26" s="25" t="n"/>
       <c r="E26" s="26" t="n">
-        <v>1421.37502</v>
+        <v>3540.32</v>
       </c>
       <c r="F26" s="26" t="n">
-        <v>1237.5</v>
+        <v>3248</v>
       </c>
       <c r="G26" s="26" t="n">
-        <v>183.87502</v>
+        <v>292.32</v>
       </c>
       <c r="H26" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="26" t="n">
-        <v>267.57813</v>
+        <v>885.08</v>
       </c>
       <c r="J26" s="26" t="n">
-        <v>0</v>
+        <v>295.02667</v>
       </c>
       <c r="K26" s="26" t="n">
-        <v>134.375</v>
+        <v>295.02667</v>
       </c>
       <c r="L26" s="26" t="n">
-        <v>133.20313</v>
+        <v>295.02667</v>
       </c>
       <c r="M26" s="26" t="n">
-        <v>392.57813</v>
+        <v>885.08</v>
       </c>
       <c r="N26" s="26" t="n">
-        <v>132.03125</v>
+        <v>295.02667</v>
       </c>
       <c r="O26" s="26" t="n">
-        <v>130.85938</v>
+        <v>295.02667</v>
       </c>
       <c r="P26" s="26" t="n">
-        <v>129.6875</v>
+        <v>295.02667</v>
       </c>
       <c r="Q26" s="26" t="n">
-        <v>389.73438</v>
+        <v>885.08</v>
       </c>
       <c r="R26" s="26" t="n">
-        <v>128.51563</v>
+        <v>295.02667</v>
       </c>
       <c r="S26" s="26" t="n">
-        <v>127.34375</v>
+        <v>295.02667</v>
       </c>
       <c r="T26" s="26" t="n">
-        <v>133.875</v>
+        <v>295.02667</v>
       </c>
       <c r="U26" s="26" t="n">
-        <v>371.48438</v>
+        <v>885.08</v>
       </c>
       <c r="V26" s="26" t="n">
-        <v>125</v>
+        <v>295.02667</v>
       </c>
       <c r="W26" s="26" t="n">
-        <v>123.82813</v>
+        <v>295.02667</v>
       </c>
       <c r="X26" s="26" t="n">
-        <v>122.65625</v>
+        <v>295.02667</v>
       </c>
     </row>
     <row r="27" ht="13" customHeight="1">
-      <c r="A27" s="14" t="inlineStr">
-        <is>
-          <t>Группа 2.1 — работа с судебными органами</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="D27" s="16" t="n"/>
-      <c r="E27" s="17" t="n">
-        <v>3217.08333</v>
-      </c>
-      <c r="F27" s="17" t="n">
-        <v>2450</v>
-      </c>
-      <c r="G27" s="17" t="n">
-        <v>767.08333</v>
-      </c>
-      <c r="H27" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="17" t="n">
-        <v>1378.75</v>
-      </c>
-      <c r="J27" s="17" t="n">
-        <v>459.58333</v>
-      </c>
-      <c r="K27" s="17" t="n">
-        <v>459.58333</v>
-      </c>
-      <c r="L27" s="17" t="n">
-        <v>459.58333</v>
-      </c>
-      <c r="M27" s="17" t="n">
-        <v>1378.75</v>
-      </c>
-      <c r="N27" s="17" t="n">
-        <v>459.58333</v>
-      </c>
-      <c r="O27" s="17" t="n">
-        <v>459.58333</v>
-      </c>
-      <c r="P27" s="17" t="n">
-        <v>459.58333</v>
-      </c>
-      <c r="Q27" s="17" t="n">
-        <v>459.58333</v>
-      </c>
-      <c r="R27" s="17" t="n">
-        <v>459.58333</v>
-      </c>
-      <c r="S27" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" s="17" t="n">
-        <v>0</v>
+      <c r="A27" s="27" t="inlineStr">
+        <is>
+          <t>в тыс. EUR (курс 101,50000)</t>
+        </is>
+      </c>
+      <c r="B27" s="28" t="n"/>
+      <c r="C27" s="28" t="n"/>
+      <c r="D27" s="29" t="n"/>
+      <c r="E27" s="30" t="n">
+        <v>34.88</v>
+      </c>
+      <c r="F27" s="30" t="n">
+        <v>32</v>
+      </c>
+      <c r="G27" s="30" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="H27" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="30" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="J27" s="30" t="n">
+        <v>2.90667</v>
+      </c>
+      <c r="K27" s="30" t="n">
+        <v>2.90667</v>
+      </c>
+      <c r="L27" s="30" t="n">
+        <v>2.90667</v>
+      </c>
+      <c r="M27" s="30" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="N27" s="30" t="n">
+        <v>2.90667</v>
+      </c>
+      <c r="O27" s="30" t="n">
+        <v>2.90667</v>
+      </c>
+      <c r="P27" s="30" t="n">
+        <v>2.90667</v>
+      </c>
+      <c r="Q27" s="30" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="R27" s="30" t="n">
+        <v>2.90667</v>
+      </c>
+      <c r="S27" s="30" t="n">
+        <v>2.90667</v>
+      </c>
+      <c r="T27" s="30" t="n">
+        <v>2.90667</v>
+      </c>
+      <c r="U27" s="30" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="V27" s="30" t="n">
+        <v>2.90667</v>
+      </c>
+      <c r="W27" s="30" t="n">
+        <v>2.90667</v>
+      </c>
+      <c r="X27" s="30" t="n">
+        <v>2.90667</v>
       </c>
     </row>
     <row r="28" ht="13" customHeight="1">
       <c r="A28" s="18" t="inlineStr">
         <is>
-          <t>ОсОО «Кемин-Курулуш»</t>
+          <t>ОсОО «Тянь-Шань Строй»</t>
         </is>
       </c>
       <c r="B28" s="19" t="n"/>
       <c r="C28" s="20" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D28" s="21" t="n"/>
       <c r="E28" s="22" t="n">
-        <v>3217.08333</v>
+        <v>1421.37502</v>
       </c>
       <c r="F28" s="22" t="n">
-        <v>2450</v>
+        <v>1237.5</v>
       </c>
       <c r="G28" s="22" t="n">
-        <v>767.08333</v>
+        <v>183.87502</v>
       </c>
       <c r="H28" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="22" t="n">
-        <v>1378.75</v>
+        <v>267.57813</v>
       </c>
       <c r="J28" s="22" t="n">
-        <v>459.58333</v>
+        <v>0</v>
       </c>
       <c r="K28" s="22" t="n">
-        <v>459.58333</v>
+        <v>134.375</v>
       </c>
       <c r="L28" s="22" t="n">
-        <v>459.58333</v>
+        <v>133.20313</v>
       </c>
       <c r="M28" s="22" t="n">
-        <v>1378.75</v>
+        <v>392.57813</v>
       </c>
       <c r="N28" s="22" t="n">
-        <v>459.58333</v>
+        <v>132.03125</v>
       </c>
       <c r="O28" s="22" t="n">
-        <v>459.58333</v>
+        <v>130.85938</v>
       </c>
       <c r="P28" s="22" t="n">
-        <v>459.58333</v>
+        <v>129.6875</v>
       </c>
       <c r="Q28" s="22" t="n">
-        <v>459.58333</v>
+        <v>389.73438</v>
       </c>
       <c r="R28" s="22" t="n">
-        <v>459.58333</v>
+        <v>128.51563</v>
       </c>
       <c r="S28" s="22" t="n">
-        <v>0</v>
+        <v>127.34375</v>
       </c>
       <c r="T28" s="22" t="n">
-        <v>0</v>
+        <v>133.875</v>
       </c>
       <c r="U28" s="22" t="n">
-        <v>0</v>
+        <v>371.48438</v>
       </c>
       <c r="V28" s="22" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="W28" s="22" t="n">
-        <v>0</v>
+        <v>123.82813</v>
       </c>
       <c r="X28" s="22" t="n">
-        <v>0</v>
+        <v>122.65625</v>
       </c>
     </row>
     <row r="29" ht="13" customHeight="1">
       <c r="A29" s="23" t="inlineStr">
         <is>
-          <t>№ 19-3/061 от 11.04.2019, USD</t>
+          <t>№ 22-1/045 от 03.02.2022, KGS</t>
         </is>
       </c>
       <c r="B29" s="24" t="n"/>
       <c r="C29" s="24" t="n"/>
-      <c r="D29" s="31" t="n">
-        <v>46218</v>
-      </c>
+      <c r="D29" s="25" t="n"/>
       <c r="E29" s="26" t="n">
-        <v>2178.75</v>
+        <v>1421.37502</v>
       </c>
       <c r="F29" s="26" t="n">
-        <v>1750</v>
+        <v>1237.5</v>
       </c>
       <c r="G29" s="26" t="n">
-        <v>428.75</v>
+        <v>183.87502</v>
       </c>
       <c r="H29" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="26" t="n">
-        <v>933.75</v>
+        <v>267.57813</v>
       </c>
       <c r="J29" s="26" t="n">
-        <v>311.25</v>
+        <v>0</v>
       </c>
       <c r="K29" s="26" t="n">
-        <v>311.25</v>
+        <v>134.375</v>
       </c>
       <c r="L29" s="26" t="n">
-        <v>311.25</v>
+        <v>133.20313</v>
       </c>
       <c r="M29" s="26" t="n">
-        <v>933.75</v>
+        <v>392.57813</v>
       </c>
       <c r="N29" s="26" t="n">
-        <v>311.25</v>
+        <v>132.03125</v>
       </c>
       <c r="O29" s="26" t="n">
-        <v>311.25</v>
+        <v>130.85938</v>
       </c>
       <c r="P29" s="26" t="n">
-        <v>311.25</v>
+        <v>129.6875</v>
       </c>
       <c r="Q29" s="26" t="n">
-        <v>311.25</v>
+        <v>389.73438</v>
       </c>
       <c r="R29" s="26" t="n">
-        <v>311.25</v>
+        <v>128.51563</v>
       </c>
       <c r="S29" s="26" t="n">
-        <v>0</v>
+        <v>127.34375</v>
       </c>
       <c r="T29" s="26" t="n">
-        <v>0</v>
+        <v>133.875</v>
       </c>
       <c r="U29" s="26" t="n">
-        <v>0</v>
+        <v>371.48438</v>
       </c>
       <c r="V29" s="26" t="n">
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="W29" s="26" t="n">
-        <v>0</v>
+        <v>123.82813</v>
       </c>
       <c r="X29" s="26" t="n">
-        <v>0</v>
+        <v>122.65625</v>
       </c>
     </row>
     <row r="30" ht="13" customHeight="1">
-      <c r="A30" s="27" t="inlineStr">
-        <is>
-          <t>в тыс. USD (курс 87,50000)</t>
-        </is>
-      </c>
-      <c r="B30" s="28" t="n"/>
-      <c r="C30" s="28" t="n"/>
-      <c r="D30" s="29" t="n"/>
-      <c r="E30" s="30" t="n">
-        <v>24.9</v>
-      </c>
-      <c r="F30" s="30" t="n">
-        <v>20</v>
-      </c>
-      <c r="G30" s="30" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="H30" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="30" t="n">
-        <v>10.67143</v>
-      </c>
-      <c r="J30" s="30" t="n">
-        <v>3.55714</v>
-      </c>
-      <c r="K30" s="30" t="n">
-        <v>3.55714</v>
-      </c>
-      <c r="L30" s="30" t="n">
-        <v>3.55714</v>
-      </c>
-      <c r="M30" s="30" t="n">
-        <v>10.67143</v>
-      </c>
-      <c r="N30" s="30" t="n">
-        <v>3.55714</v>
-      </c>
-      <c r="O30" s="30" t="n">
-        <v>3.55714</v>
-      </c>
-      <c r="P30" s="30" t="n">
-        <v>3.55714</v>
-      </c>
-      <c r="Q30" s="30" t="n">
-        <v>3.55714</v>
-      </c>
-      <c r="R30" s="30" t="n">
-        <v>3.55714</v>
-      </c>
-      <c r="S30" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" s="30" t="n">
+      <c r="A30" s="14" t="inlineStr">
+        <is>
+          <t>Группа 2.1 — работа с судебными органами</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" s="16" t="n"/>
+      <c r="E30" s="17" t="n">
+        <v>3217.08333</v>
+      </c>
+      <c r="F30" s="17" t="n">
+        <v>2450</v>
+      </c>
+      <c r="G30" s="17" t="n">
+        <v>767.08333</v>
+      </c>
+      <c r="H30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="17" t="n">
+        <v>1378.75</v>
+      </c>
+      <c r="J30" s="17" t="n">
+        <v>459.58333</v>
+      </c>
+      <c r="K30" s="17" t="n">
+        <v>459.58333</v>
+      </c>
+      <c r="L30" s="17" t="n">
+        <v>459.58333</v>
+      </c>
+      <c r="M30" s="17" t="n">
+        <v>1378.75</v>
+      </c>
+      <c r="N30" s="17" t="n">
+        <v>459.58333</v>
+      </c>
+      <c r="O30" s="17" t="n">
+        <v>459.58333</v>
+      </c>
+      <c r="P30" s="17" t="n">
+        <v>459.58333</v>
+      </c>
+      <c r="Q30" s="17" t="n">
+        <v>459.58333</v>
+      </c>
+      <c r="R30" s="17" t="n">
+        <v>459.58333</v>
+      </c>
+      <c r="S30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31" ht="13" customHeight="1">
-      <c r="A31" s="23" t="inlineStr">
-        <is>
-          <t>№ 22-3/014 от 18.03.2022, KGS</t>
-        </is>
-      </c>
-      <c r="B31" s="24" t="n"/>
-      <c r="C31" s="24" t="n"/>
-      <c r="D31" s="31" t="n">
-        <v>46218</v>
-      </c>
-      <c r="E31" s="26" t="n">
-        <v>933.33333</v>
-      </c>
-      <c r="F31" s="26" t="n">
-        <v>700</v>
-      </c>
-      <c r="G31" s="26" t="n">
-        <v>233.33333</v>
-      </c>
-      <c r="H31" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="26" t="n">
-        <v>400</v>
-      </c>
-      <c r="J31" s="26" t="n">
-        <v>133.33333</v>
-      </c>
-      <c r="K31" s="26" t="n">
-        <v>133.33333</v>
-      </c>
-      <c r="L31" s="26" t="n">
-        <v>133.33333</v>
-      </c>
-      <c r="M31" s="26" t="n">
-        <v>400</v>
-      </c>
-      <c r="N31" s="26" t="n">
-        <v>133.33333</v>
-      </c>
-      <c r="O31" s="26" t="n">
-        <v>133.33333</v>
-      </c>
-      <c r="P31" s="26" t="n">
-        <v>133.33333</v>
-      </c>
-      <c r="Q31" s="26" t="n">
-        <v>133.33333</v>
-      </c>
-      <c r="R31" s="26" t="n">
-        <v>133.33333</v>
-      </c>
-      <c r="S31" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" s="26" t="n">
+      <c r="A31" s="18" t="inlineStr">
+        <is>
+          <t>ОсОО «Кемин-Курулуш»</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="n"/>
+      <c r="C31" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" s="21" t="n"/>
+      <c r="E31" s="22" t="n">
+        <v>3217.08333</v>
+      </c>
+      <c r="F31" s="22" t="n">
+        <v>2450</v>
+      </c>
+      <c r="G31" s="22" t="n">
+        <v>767.08333</v>
+      </c>
+      <c r="H31" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="22" t="n">
+        <v>1378.75</v>
+      </c>
+      <c r="J31" s="22" t="n">
+        <v>459.58333</v>
+      </c>
+      <c r="K31" s="22" t="n">
+        <v>459.58333</v>
+      </c>
+      <c r="L31" s="22" t="n">
+        <v>459.58333</v>
+      </c>
+      <c r="M31" s="22" t="n">
+        <v>1378.75</v>
+      </c>
+      <c r="N31" s="22" t="n">
+        <v>459.58333</v>
+      </c>
+      <c r="O31" s="22" t="n">
+        <v>459.58333</v>
+      </c>
+      <c r="P31" s="22" t="n">
+        <v>459.58333</v>
+      </c>
+      <c r="Q31" s="22" t="n">
+        <v>459.58333</v>
+      </c>
+      <c r="R31" s="22" t="n">
+        <v>459.58333</v>
+      </c>
+      <c r="S31" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32" ht="13" customHeight="1">
       <c r="A32" s="23" t="inlineStr">
         <is>
-          <t>№ 24-3/105 от 02.12.2024, KGS</t>
+          <t>№ 19-3/061 от 11.04.2019, USD</t>
         </is>
       </c>
       <c r="B32" s="24" t="n"/>
@@ -2659,46 +2657,46 @@
         <v>46218</v>
       </c>
       <c r="E32" s="26" t="n">
-        <v>105</v>
+        <v>2178.75</v>
       </c>
       <c r="F32" s="26" t="n">
-        <v>0</v>
+        <v>1750</v>
       </c>
       <c r="G32" s="26" t="n">
-        <v>105</v>
+        <v>428.75</v>
       </c>
       <c r="H32" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="26" t="n">
-        <v>45</v>
+        <v>933.75</v>
       </c>
       <c r="J32" s="26" t="n">
-        <v>15</v>
+        <v>311.25</v>
       </c>
       <c r="K32" s="26" t="n">
-        <v>15</v>
+        <v>311.25</v>
       </c>
       <c r="L32" s="26" t="n">
-        <v>15</v>
+        <v>311.25</v>
       </c>
       <c r="M32" s="26" t="n">
-        <v>45</v>
+        <v>933.75</v>
       </c>
       <c r="N32" s="26" t="n">
-        <v>15</v>
+        <v>311.25</v>
       </c>
       <c r="O32" s="26" t="n">
-        <v>15</v>
+        <v>311.25</v>
       </c>
       <c r="P32" s="26" t="n">
-        <v>15</v>
+        <v>311.25</v>
       </c>
       <c r="Q32" s="26" t="n">
-        <v>15</v>
+        <v>311.25</v>
       </c>
       <c r="R32" s="26" t="n">
-        <v>15</v>
+        <v>311.25</v>
       </c>
       <c r="S32" s="26" t="n">
         <v>0</v>
@@ -2720,187 +2718,199 @@
       </c>
     </row>
     <row r="33" ht="13" customHeight="1">
-      <c r="A33" s="14" t="inlineStr">
-        <is>
-          <t>Группа 4 — безнадёжные долги</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D33" s="16" t="n"/>
-      <c r="E33" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" s="32" t="n"/>
-      <c r="V33" s="32" t="n"/>
-      <c r="W33" s="32" t="n"/>
-      <c r="X33" s="32" t="n"/>
+      <c r="A33" s="27" t="inlineStr">
+        <is>
+          <t>в тыс. USD (курс 87,50000)</t>
+        </is>
+      </c>
+      <c r="B33" s="28" t="n"/>
+      <c r="C33" s="28" t="n"/>
+      <c r="D33" s="29" t="n"/>
+      <c r="E33" s="30" t="n">
+        <v>24.9</v>
+      </c>
+      <c r="F33" s="30" t="n">
+        <v>20</v>
+      </c>
+      <c r="G33" s="30" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H33" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="30" t="n">
+        <v>10.67143</v>
+      </c>
+      <c r="J33" s="30" t="n">
+        <v>3.55714</v>
+      </c>
+      <c r="K33" s="30" t="n">
+        <v>3.55714</v>
+      </c>
+      <c r="L33" s="30" t="n">
+        <v>3.55714</v>
+      </c>
+      <c r="M33" s="30" t="n">
+        <v>10.67143</v>
+      </c>
+      <c r="N33" s="30" t="n">
+        <v>3.55714</v>
+      </c>
+      <c r="O33" s="30" t="n">
+        <v>3.55714</v>
+      </c>
+      <c r="P33" s="30" t="n">
+        <v>3.55714</v>
+      </c>
+      <c r="Q33" s="30" t="n">
+        <v>3.55714</v>
+      </c>
+      <c r="R33" s="30" t="n">
+        <v>3.55714</v>
+      </c>
+      <c r="S33" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" s="30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34" ht="13" customHeight="1">
-      <c r="A34" s="18" t="inlineStr">
-        <is>
-          <t>ОсОО «Тянь-Шань Металл»</t>
-        </is>
-      </c>
-      <c r="B34" s="19" t="n"/>
-      <c r="C34" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D34" s="21" t="n"/>
-      <c r="E34" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R34" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" s="19" t="n"/>
-      <c r="V34" s="19" t="n"/>
-      <c r="W34" s="19" t="n"/>
-      <c r="X34" s="19" t="n"/>
+      <c r="A34" s="23" t="inlineStr">
+        <is>
+          <t>№ 22-3/014 от 18.03.2022, KGS</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="n"/>
+      <c r="C34" s="24" t="n"/>
+      <c r="D34" s="31" t="n">
+        <v>46218</v>
+      </c>
+      <c r="E34" s="26" t="n">
+        <v>933.33333</v>
+      </c>
+      <c r="F34" s="26" t="n">
+        <v>700</v>
+      </c>
+      <c r="G34" s="26" t="n">
+        <v>233.33333</v>
+      </c>
+      <c r="H34" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="26" t="n">
+        <v>400</v>
+      </c>
+      <c r="J34" s="26" t="n">
+        <v>133.33333</v>
+      </c>
+      <c r="K34" s="26" t="n">
+        <v>133.33333</v>
+      </c>
+      <c r="L34" s="26" t="n">
+        <v>133.33333</v>
+      </c>
+      <c r="M34" s="26" t="n">
+        <v>400</v>
+      </c>
+      <c r="N34" s="26" t="n">
+        <v>133.33333</v>
+      </c>
+      <c r="O34" s="26" t="n">
+        <v>133.33333</v>
+      </c>
+      <c r="P34" s="26" t="n">
+        <v>133.33333</v>
+      </c>
+      <c r="Q34" s="26" t="n">
+        <v>133.33333</v>
+      </c>
+      <c r="R34" s="26" t="n">
+        <v>133.33333</v>
+      </c>
+      <c r="S34" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35" ht="13" customHeight="1">
       <c r="A35" s="23" t="inlineStr">
         <is>
-          <t>№ 20-3/052 от 21.07.2020, KGS</t>
+          <t>№ 24-3/105 от 02.12.2024, KGS</t>
         </is>
       </c>
       <c r="B35" s="24" t="n"/>
       <c r="C35" s="24" t="n"/>
       <c r="D35" s="31" t="n">
-        <v>46283</v>
+        <v>46218</v>
       </c>
       <c r="E35" s="26" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F35" s="26" t="n">
         <v>0</v>
       </c>
       <c r="G35" s="26" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="H35" s="26" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="26" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J35" s="26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="K35" s="26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="L35" s="26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M35" s="26" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="N35" s="26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O35" s="26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="P35" s="26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q35" s="26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R35" s="26" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="S35" s="26" t="n">
         <v>0</v>
@@ -2908,15 +2918,23 @@
       <c r="T35" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="U35" s="24" t="n"/>
-      <c r="V35" s="24" t="n"/>
-      <c r="W35" s="24" t="n"/>
-      <c r="X35" s="24" t="n"/>
+      <c r="U35" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" s="26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36" ht="13" customHeight="1">
       <c r="A36" s="14" t="inlineStr">
         <is>
-          <t>Группа 5 — погашенные</t>
+          <t>Группа 5.1 — погашенные</t>
         </is>
       </c>
       <c r="B36" s="15" t="n">
@@ -3060,955 +3078,933 @@
       <c r="X38" s="24" t="n"/>
     </row>
     <row r="39" ht="13" customHeight="1">
-      <c r="A39" s="10" t="inlineStr">
+      <c r="A39" s="14" t="inlineStr">
+        <is>
+          <t>Группа 5.2 — списанные</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" s="16" t="n"/>
+      <c r="E39" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" s="32" t="n"/>
+      <c r="V39" s="32" t="n"/>
+      <c r="W39" s="32" t="n"/>
+      <c r="X39" s="32" t="n"/>
+    </row>
+    <row r="40" ht="13" customHeight="1">
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>ОсОО «Тянь-Шань Металл»</t>
+        </is>
+      </c>
+      <c r="B40" s="19" t="n"/>
+      <c r="C40" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" s="21" t="n"/>
+      <c r="E40" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" s="19" t="n"/>
+      <c r="V40" s="19" t="n"/>
+      <c r="W40" s="19" t="n"/>
+      <c r="X40" s="19" t="n"/>
+    </row>
+    <row r="41" ht="13" customHeight="1">
+      <c r="A41" s="23" t="inlineStr">
+        <is>
+          <t>№ 20-3/052 от 21.07.2020, KGS</t>
+        </is>
+      </c>
+      <c r="B41" s="24" t="n"/>
+      <c r="C41" s="24" t="n"/>
+      <c r="D41" s="31" t="n">
+        <v>46283</v>
+      </c>
+      <c r="E41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" s="24" t="n"/>
+      <c r="V41" s="24" t="n"/>
+      <c r="W41" s="24" t="n"/>
+      <c r="X41" s="24" t="n"/>
+    </row>
+    <row r="42" ht="13" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
         <is>
           <t>Департамент регионального развития</t>
         </is>
       </c>
-      <c r="B39" s="11" t="n">
+      <c r="B42" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="C39" s="11" t="n">
+      <c r="C42" s="11" t="n">
         <v>14</v>
       </c>
-      <c r="D39" s="12" t="n"/>
-      <c r="E39" s="13" t="n">
+      <c r="D42" s="12" t="n"/>
+      <c r="E42" s="13" t="n">
         <v>8307.488139999999</v>
       </c>
-      <c r="F39" s="13" t="n">
+      <c r="F42" s="13" t="n">
         <v>6468.2381</v>
       </c>
-      <c r="G39" s="13" t="n">
+      <c r="G42" s="13" t="n">
         <v>1788.70003</v>
       </c>
-      <c r="H39" s="13" t="n">
+      <c r="H42" s="13" t="n">
         <v>50.55001</v>
       </c>
-      <c r="I39" s="13" t="n">
+      <c r="I42" s="13" t="n">
         <v>1824.20537</v>
       </c>
-      <c r="J39" s="13" t="n">
+      <c r="J42" s="13" t="n">
         <v>512.26846</v>
       </c>
-      <c r="K39" s="13" t="n">
+      <c r="K42" s="13" t="n">
         <v>511.40179</v>
       </c>
-      <c r="L39" s="13" t="n">
+      <c r="L42" s="13" t="n">
         <v>800.53512</v>
       </c>
-      <c r="M39" s="13" t="n">
+      <c r="M42" s="13" t="n">
         <v>2119.65537</v>
       </c>
-      <c r="N39" s="13" t="n">
+      <c r="N42" s="13" t="n">
         <v>628.00179</v>
       </c>
-      <c r="O39" s="13" t="n">
+      <c r="O42" s="13" t="n">
         <v>626.7184600000001</v>
       </c>
-      <c r="P39" s="13" t="n">
+      <c r="P42" s="13" t="n">
         <v>864.93512</v>
       </c>
-      <c r="Q39" s="13" t="n">
-        <v>1843.73453</v>
-      </c>
-      <c r="R39" s="13" t="n">
+      <c r="Q42" s="13" t="n">
+        <v>1843.73454</v>
+      </c>
+      <c r="R42" s="13" t="n">
         <v>583.65179</v>
       </c>
-      <c r="S39" s="13" t="n">
+      <c r="S42" s="13" t="n">
         <v>582.36846</v>
       </c>
-      <c r="T39" s="13" t="n">
+      <c r="T42" s="13" t="n">
         <v>677.71429</v>
       </c>
-      <c r="U39" s="13" t="n">
+      <c r="U42" s="13" t="n">
         <v>2519.89287</v>
       </c>
-      <c r="V39" s="13" t="n">
-        <v>841.24762</v>
-      </c>
-      <c r="W39" s="13" t="n">
-        <v>839.96429</v>
-      </c>
-      <c r="X39" s="13" t="n">
-        <v>838.6809500000001</v>
-      </c>
-    </row>
-    <row r="40" ht="13" customHeight="1">
-      <c r="A40" s="14" t="inlineStr">
+      <c r="V42" s="13" t="n">
+        <v>841.24763</v>
+      </c>
+      <c r="W42" s="13" t="n">
+        <v>839.9643</v>
+      </c>
+      <c r="X42" s="13" t="n">
+        <v>838.68096</v>
+      </c>
+    </row>
+    <row r="43" ht="13" customHeight="1">
+      <c r="A43" s="14" t="inlineStr">
         <is>
           <t>Группа 1.1 — погашают по графику</t>
         </is>
       </c>
-      <c r="B40" s="15" t="n">
+      <c r="B43" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="C40" s="15" t="n">
+      <c r="C43" s="15" t="n">
         <v>6</v>
       </c>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="17" t="n">
+      <c r="D43" s="16" t="n"/>
+      <c r="E43" s="17" t="n">
         <v>3182.50004</v>
       </c>
-      <c r="F40" s="17" t="n">
+      <c r="F43" s="17" t="n">
         <v>2225</v>
       </c>
-      <c r="G40" s="17" t="n">
+      <c r="G43" s="17" t="n">
         <v>957.50004</v>
       </c>
-      <c r="H40" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="17" t="n">
+      <c r="H43" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="17" t="n">
         <v>507.50001</v>
       </c>
-      <c r="J40" s="17" t="n">
+      <c r="J43" s="17" t="n">
         <v>170.00001</v>
       </c>
-      <c r="K40" s="17" t="n">
+      <c r="K43" s="17" t="n">
         <v>169.16667</v>
       </c>
-      <c r="L40" s="17" t="n">
+      <c r="L43" s="17" t="n">
         <v>168.33333</v>
       </c>
-      <c r="M40" s="17" t="n">
+      <c r="M43" s="17" t="n">
         <v>853.75001</v>
       </c>
-      <c r="N40" s="17" t="n">
+      <c r="N43" s="17" t="n">
         <v>285.83334</v>
       </c>
-      <c r="O40" s="17" t="n">
+      <c r="O43" s="17" t="n">
         <v>284.58334</v>
       </c>
-      <c r="P40" s="17" t="n">
+      <c r="P43" s="17" t="n">
         <v>283.33333</v>
       </c>
-      <c r="Q40" s="17" t="n">
+      <c r="Q43" s="17" t="n">
         <v>842.50001</v>
       </c>
-      <c r="R40" s="17" t="n">
+      <c r="R43" s="17" t="n">
         <v>282.08334</v>
       </c>
-      <c r="S40" s="17" t="n">
+      <c r="S43" s="17" t="n">
         <v>280.83334</v>
       </c>
-      <c r="T40" s="17" t="n">
+      <c r="T43" s="17" t="n">
         <v>279.58333</v>
       </c>
-      <c r="U40" s="17" t="n">
+      <c r="U43" s="17" t="n">
         <v>978.75001</v>
       </c>
-      <c r="V40" s="17" t="n">
+      <c r="V43" s="17" t="n">
         <v>327.50001</v>
       </c>
-      <c r="W40" s="17" t="n">
+      <c r="W43" s="17" t="n">
         <v>326.25001</v>
       </c>
-      <c r="X40" s="17" t="n">
+      <c r="X43" s="17" t="n">
         <v>325</v>
       </c>
     </row>
-    <row r="41" ht="13" customHeight="1">
-      <c r="A41" s="18" t="inlineStr">
+    <row r="44" ht="13" customHeight="1">
+      <c r="A44" s="18" t="inlineStr">
         <is>
           <t>ОсОО «Ак-Булак»</t>
         </is>
       </c>
-      <c r="B41" s="19" t="n"/>
-      <c r="C41" s="20" t="n">
+      <c r="B44" s="19" t="n"/>
+      <c r="C44" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D41" s="21" t="n"/>
-      <c r="E41" s="22" t="n">
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="22" t="n">
         <v>907.5</v>
       </c>
-      <c r="F41" s="22" t="n">
+      <c r="F44" s="22" t="n">
         <v>600</v>
       </c>
-      <c r="G41" s="22" t="n">
+      <c r="G44" s="22" t="n">
         <v>307.5</v>
       </c>
-      <c r="H41" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="22" t="n">
+      <c r="H44" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="22" t="n">
         <v>232.5</v>
       </c>
-      <c r="J41" s="22" t="n">
+      <c r="J44" s="22" t="n">
         <v>77.91667</v>
       </c>
-      <c r="K41" s="22" t="n">
+      <c r="K44" s="22" t="n">
         <v>77.5</v>
       </c>
-      <c r="L41" s="22" t="n">
+      <c r="L44" s="22" t="n">
         <v>77.08333</v>
       </c>
-      <c r="M41" s="22" t="n">
+      <c r="M44" s="22" t="n">
         <v>228.75</v>
       </c>
-      <c r="N41" s="22" t="n">
+      <c r="N44" s="22" t="n">
         <v>76.66667</v>
       </c>
-      <c r="O41" s="22" t="n">
+      <c r="O44" s="22" t="n">
         <v>76.25</v>
       </c>
-      <c r="P41" s="22" t="n">
+      <c r="P44" s="22" t="n">
         <v>75.83333</v>
       </c>
-      <c r="Q41" s="22" t="n">
+      <c r="Q44" s="22" t="n">
         <v>225</v>
       </c>
-      <c r="R41" s="22" t="n">
+      <c r="R44" s="22" t="n">
         <v>75.41667</v>
       </c>
-      <c r="S41" s="22" t="n">
+      <c r="S44" s="22" t="n">
         <v>75</v>
       </c>
-      <c r="T41" s="22" t="n">
+      <c r="T44" s="22" t="n">
         <v>74.58333</v>
       </c>
-      <c r="U41" s="22" t="n">
+      <c r="U44" s="22" t="n">
         <v>221.25</v>
       </c>
-      <c r="V41" s="22" t="n">
+      <c r="V44" s="22" t="n">
         <v>74.16667</v>
       </c>
-      <c r="W41" s="22" t="n">
+      <c r="W44" s="22" t="n">
         <v>73.75</v>
       </c>
-      <c r="X41" s="22" t="n">
+      <c r="X44" s="22" t="n">
         <v>73.33333</v>
       </c>
     </row>
-    <row r="42" ht="13" customHeight="1">
-      <c r="A42" s="23" t="inlineStr">
+    <row r="45" ht="13" customHeight="1">
+      <c r="A45" s="23" t="inlineStr">
         <is>
           <t>№ 24-6/019 от 11.02.2024, KGS</t>
         </is>
       </c>
-      <c r="B42" s="24" t="n"/>
-      <c r="C42" s="24" t="n"/>
-      <c r="D42" s="25" t="n"/>
-      <c r="E42" s="26" t="n">
+      <c r="B45" s="24" t="n"/>
+      <c r="C45" s="24" t="n"/>
+      <c r="D45" s="25" t="n"/>
+      <c r="E45" s="26" t="n">
         <v>907.5</v>
       </c>
-      <c r="F42" s="26" t="n">
+      <c r="F45" s="26" t="n">
         <v>600</v>
       </c>
-      <c r="G42" s="26" t="n">
+      <c r="G45" s="26" t="n">
         <v>307.5</v>
       </c>
-      <c r="H42" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="26" t="n">
+      <c r="H45" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="26" t="n">
         <v>232.5</v>
       </c>
-      <c r="J42" s="26" t="n">
+      <c r="J45" s="26" t="n">
         <v>77.91667</v>
       </c>
-      <c r="K42" s="26" t="n">
+      <c r="K45" s="26" t="n">
         <v>77.5</v>
       </c>
-      <c r="L42" s="26" t="n">
+      <c r="L45" s="26" t="n">
         <v>77.08333</v>
       </c>
-      <c r="M42" s="26" t="n">
+      <c r="M45" s="26" t="n">
         <v>228.75</v>
       </c>
-      <c r="N42" s="26" t="n">
+      <c r="N45" s="26" t="n">
         <v>76.66667</v>
       </c>
-      <c r="O42" s="26" t="n">
+      <c r="O45" s="26" t="n">
         <v>76.25</v>
       </c>
-      <c r="P42" s="26" t="n">
+      <c r="P45" s="26" t="n">
         <v>75.83333</v>
       </c>
-      <c r="Q42" s="26" t="n">
+      <c r="Q45" s="26" t="n">
         <v>225</v>
       </c>
-      <c r="R42" s="26" t="n">
+      <c r="R45" s="26" t="n">
         <v>75.41667</v>
       </c>
-      <c r="S42" s="26" t="n">
+      <c r="S45" s="26" t="n">
         <v>75</v>
       </c>
-      <c r="T42" s="26" t="n">
+      <c r="T45" s="26" t="n">
         <v>74.58333</v>
       </c>
-      <c r="U42" s="26" t="n">
+      <c r="U45" s="26" t="n">
         <v>221.25</v>
       </c>
-      <c r="V42" s="26" t="n">
+      <c r="V45" s="26" t="n">
         <v>74.16667</v>
       </c>
-      <c r="W42" s="26" t="n">
+      <c r="W45" s="26" t="n">
         <v>73.75</v>
       </c>
-      <c r="X42" s="26" t="n">
+      <c r="X45" s="26" t="n">
         <v>73.33333</v>
       </c>
     </row>
-    <row r="43" ht="13" customHeight="1">
-      <c r="A43" s="18" t="inlineStr">
+    <row r="46" ht="13" customHeight="1">
+      <c r="A46" s="18" t="inlineStr">
         <is>
           <t>ОсОО «Ала-Тоо Агро»</t>
         </is>
       </c>
-      <c r="B43" s="19" t="n"/>
-      <c r="C43" s="20" t="n">
+      <c r="B46" s="19" t="n"/>
+      <c r="C46" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D43" s="21" t="n"/>
-      <c r="E43" s="22" t="n">
+      <c r="D46" s="21" t="n"/>
+      <c r="E46" s="22" t="n">
         <v>1050</v>
       </c>
-      <c r="F43" s="22" t="n">
+      <c r="F46" s="22" t="n">
         <v>900</v>
       </c>
-      <c r="G43" s="22" t="n">
+      <c r="G46" s="22" t="n">
         <v>150</v>
       </c>
-      <c r="H43" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="22" t="n">
+      <c r="H46" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="22" t="n">
         <v>353.75</v>
       </c>
-      <c r="N43" s="22" t="n">
+      <c r="N46" s="22" t="n">
         <v>118.33333</v>
       </c>
-      <c r="O43" s="22" t="n">
+      <c r="O46" s="22" t="n">
         <v>117.91667</v>
       </c>
-      <c r="P43" s="22" t="n">
+      <c r="P46" s="22" t="n">
         <v>117.5</v>
       </c>
-      <c r="Q43" s="22" t="n">
+      <c r="Q46" s="22" t="n">
         <v>350</v>
       </c>
-      <c r="R43" s="22" t="n">
+      <c r="R46" s="22" t="n">
         <v>117.08333</v>
       </c>
-      <c r="S43" s="22" t="n">
+      <c r="S46" s="22" t="n">
         <v>116.66667</v>
       </c>
-      <c r="T43" s="22" t="n">
+      <c r="T46" s="22" t="n">
         <v>116.25</v>
       </c>
-      <c r="U43" s="22" t="n">
+      <c r="U46" s="22" t="n">
         <v>346.25</v>
       </c>
-      <c r="V43" s="22" t="n">
+      <c r="V46" s="22" t="n">
         <v>115.83333</v>
       </c>
-      <c r="W43" s="22" t="n">
+      <c r="W46" s="22" t="n">
         <v>115.41667</v>
       </c>
-      <c r="X43" s="22" t="n">
+      <c r="X46" s="22" t="n">
         <v>115</v>
       </c>
     </row>
-    <row r="44" ht="13" customHeight="1">
-      <c r="A44" s="23" t="inlineStr">
+    <row r="47" ht="13" customHeight="1">
+      <c r="A47" s="23" t="inlineStr">
         <is>
           <t>№ 25-4/030 от 10.02.2025, KGS</t>
         </is>
       </c>
-      <c r="B44" s="24" t="n"/>
-      <c r="C44" s="24" t="n"/>
-      <c r="D44" s="25" t="n"/>
-      <c r="E44" s="26" t="n">
+      <c r="B47" s="24" t="n"/>
+      <c r="C47" s="24" t="n"/>
+      <c r="D47" s="25" t="n"/>
+      <c r="E47" s="26" t="n">
         <v>1050</v>
       </c>
-      <c r="F44" s="26" t="n">
+      <c r="F47" s="26" t="n">
         <v>900</v>
       </c>
-      <c r="G44" s="26" t="n">
+      <c r="G47" s="26" t="n">
         <v>150</v>
       </c>
-      <c r="H44" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" s="26" t="n">
+      <c r="H47" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="26" t="n">
         <v>353.75</v>
       </c>
-      <c r="N44" s="26" t="n">
+      <c r="N47" s="26" t="n">
         <v>118.33333</v>
       </c>
-      <c r="O44" s="26" t="n">
+      <c r="O47" s="26" t="n">
         <v>117.91667</v>
       </c>
-      <c r="P44" s="26" t="n">
+      <c r="P47" s="26" t="n">
         <v>117.5</v>
       </c>
-      <c r="Q44" s="26" t="n">
+      <c r="Q47" s="26" t="n">
         <v>350</v>
       </c>
-      <c r="R44" s="26" t="n">
+      <c r="R47" s="26" t="n">
         <v>117.08333</v>
       </c>
-      <c r="S44" s="26" t="n">
+      <c r="S47" s="26" t="n">
         <v>116.66667</v>
       </c>
-      <c r="T44" s="26" t="n">
+      <c r="T47" s="26" t="n">
         <v>116.25</v>
       </c>
-      <c r="U44" s="26" t="n">
+      <c r="U47" s="26" t="n">
         <v>346.25</v>
       </c>
-      <c r="V44" s="26" t="n">
+      <c r="V47" s="26" t="n">
         <v>115.83333</v>
       </c>
-      <c r="W44" s="26" t="n">
+      <c r="W47" s="26" t="n">
         <v>115.41667</v>
       </c>
-      <c r="X44" s="26" t="n">
+      <c r="X47" s="26" t="n">
         <v>115</v>
       </c>
     </row>
-    <row r="45" ht="13" customHeight="1">
-      <c r="A45" s="18" t="inlineStr">
+    <row r="48" ht="13" customHeight="1">
+      <c r="A48" s="18" t="inlineStr">
         <is>
           <t>ОсОО «Алтын-Тоо»</t>
         </is>
       </c>
-      <c r="B45" s="19" t="n"/>
-      <c r="C45" s="20" t="n">
+      <c r="B48" s="19" t="n"/>
+      <c r="C48" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D45" s="21" t="n"/>
-      <c r="E45" s="22" t="n">
+      <c r="D48" s="21" t="n"/>
+      <c r="E48" s="22" t="n">
         <v>200.00004</v>
       </c>
-      <c r="F45" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="22" t="n">
+      <c r="F48" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="22" t="n">
         <v>200.00004</v>
       </c>
-      <c r="H45" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="22" t="n">
+      <c r="H48" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="22" t="n">
         <v>50.00001</v>
       </c>
-      <c r="J45" s="22" t="n">
+      <c r="J48" s="22" t="n">
         <v>16.66667</v>
       </c>
-      <c r="K45" s="22" t="n">
+      <c r="K48" s="22" t="n">
         <v>16.66667</v>
       </c>
-      <c r="L45" s="22" t="n">
+      <c r="L48" s="22" t="n">
         <v>16.66667</v>
       </c>
-      <c r="M45" s="22" t="n">
+      <c r="M48" s="22" t="n">
         <v>50.00001</v>
       </c>
-      <c r="N45" s="22" t="n">
+      <c r="N48" s="22" t="n">
         <v>16.66667</v>
       </c>
-      <c r="O45" s="22" t="n">
+      <c r="O48" s="22" t="n">
         <v>16.66667</v>
       </c>
-      <c r="P45" s="22" t="n">
+      <c r="P48" s="22" t="n">
         <v>16.66667</v>
       </c>
-      <c r="Q45" s="22" t="n">
+      <c r="Q48" s="22" t="n">
         <v>50.00001</v>
       </c>
-      <c r="R45" s="22" t="n">
+      <c r="R48" s="22" t="n">
         <v>16.66667</v>
       </c>
-      <c r="S45" s="22" t="n">
+      <c r="S48" s="22" t="n">
         <v>16.66667</v>
       </c>
-      <c r="T45" s="22" t="n">
+      <c r="T48" s="22" t="n">
         <v>16.66667</v>
       </c>
-      <c r="U45" s="22" t="n">
+      <c r="U48" s="22" t="n">
         <v>50.00001</v>
       </c>
-      <c r="V45" s="22" t="n">
+      <c r="V48" s="22" t="n">
         <v>16.66667</v>
       </c>
-      <c r="W45" s="22" t="n">
+      <c r="W48" s="22" t="n">
         <v>16.66667</v>
       </c>
-      <c r="X45" s="22" t="n">
+      <c r="X48" s="22" t="n">
         <v>16.66667</v>
       </c>
     </row>
-    <row r="46" ht="13" customHeight="1">
-      <c r="A46" s="23" t="inlineStr">
+    <row r="49" ht="13" customHeight="1">
+      <c r="A49" s="23" t="inlineStr">
         <is>
           <t>№ 24-2/088 от 12.03.2024, KGS</t>
         </is>
       </c>
-      <c r="B46" s="24" t="n"/>
-      <c r="C46" s="24" t="n"/>
-      <c r="D46" s="25" t="n"/>
-      <c r="E46" s="26" t="n">
+      <c r="B49" s="24" t="n"/>
+      <c r="C49" s="24" t="n"/>
+      <c r="D49" s="25" t="n"/>
+      <c r="E49" s="26" t="n">
         <v>200.00004</v>
       </c>
-      <c r="F46" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="26" t="n">
+      <c r="F49" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="26" t="n">
         <v>200.00004</v>
       </c>
-      <c r="H46" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="26" t="n">
+      <c r="H49" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="26" t="n">
         <v>50.00001</v>
       </c>
-      <c r="J46" s="26" t="n">
+      <c r="J49" s="26" t="n">
         <v>16.66667</v>
       </c>
-      <c r="K46" s="26" t="n">
+      <c r="K49" s="26" t="n">
         <v>16.66667</v>
       </c>
-      <c r="L46" s="26" t="n">
+      <c r="L49" s="26" t="n">
         <v>16.66667</v>
       </c>
-      <c r="M46" s="26" t="n">
+      <c r="M49" s="26" t="n">
         <v>50.00001</v>
       </c>
-      <c r="N46" s="26" t="n">
+      <c r="N49" s="26" t="n">
         <v>16.66667</v>
       </c>
-      <c r="O46" s="26" t="n">
+      <c r="O49" s="26" t="n">
         <v>16.66667</v>
       </c>
-      <c r="P46" s="26" t="n">
+      <c r="P49" s="26" t="n">
         <v>16.66667</v>
       </c>
-      <c r="Q46" s="26" t="n">
+      <c r="Q49" s="26" t="n">
         <v>50.00001</v>
       </c>
-      <c r="R46" s="26" t="n">
+      <c r="R49" s="26" t="n">
         <v>16.66667</v>
       </c>
-      <c r="S46" s="26" t="n">
+      <c r="S49" s="26" t="n">
         <v>16.66667</v>
       </c>
-      <c r="T46" s="26" t="n">
+      <c r="T49" s="26" t="n">
         <v>16.66667</v>
       </c>
-      <c r="U46" s="26" t="n">
+      <c r="U49" s="26" t="n">
         <v>50.00001</v>
       </c>
-      <c r="V46" s="26" t="n">
+      <c r="V49" s="26" t="n">
         <v>16.66667</v>
       </c>
-      <c r="W46" s="26" t="n">
+      <c r="W49" s="26" t="n">
         <v>16.66667</v>
       </c>
-      <c r="X46" s="26" t="n">
+      <c r="X49" s="26" t="n">
         <v>16.66667</v>
       </c>
     </row>
-    <row r="47" ht="13" customHeight="1">
-      <c r="A47" s="18" t="inlineStr">
+    <row r="50" ht="13" customHeight="1">
+      <c r="A50" s="18" t="inlineStr">
         <is>
           <t>ОсОО «Достук Строй»</t>
         </is>
       </c>
-      <c r="B47" s="19" t="n"/>
-      <c r="C47" s="20" t="n">
+      <c r="B50" s="19" t="n"/>
+      <c r="C50" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D47" s="21" t="n"/>
-      <c r="E47" s="22" t="n">
+      <c r="D50" s="21" t="n"/>
+      <c r="E50" s="22" t="n">
         <v>147.5</v>
       </c>
-      <c r="F47" s="22" t="n">
+      <c r="F50" s="22" t="n">
         <v>125</v>
       </c>
-      <c r="G47" s="22" t="n">
+      <c r="G50" s="22" t="n">
         <v>22.5</v>
       </c>
-      <c r="H47" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="19" t="n"/>
-      <c r="J47" s="19" t="n"/>
-      <c r="K47" s="19" t="n"/>
-      <c r="L47" s="19" t="n"/>
-      <c r="M47" s="19" t="n"/>
-      <c r="N47" s="19" t="n"/>
-      <c r="O47" s="19" t="n"/>
-      <c r="P47" s="19" t="n"/>
-      <c r="Q47" s="19" t="n"/>
-      <c r="R47" s="19" t="n"/>
-      <c r="S47" s="19" t="n"/>
-      <c r="T47" s="19" t="n"/>
-      <c r="U47" s="22" t="n">
+      <c r="H50" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="19" t="n"/>
+      <c r="J50" s="19" t="n"/>
+      <c r="K50" s="19" t="n"/>
+      <c r="L50" s="19" t="n"/>
+      <c r="M50" s="19" t="n"/>
+      <c r="N50" s="19" t="n"/>
+      <c r="O50" s="19" t="n"/>
+      <c r="P50" s="19" t="n"/>
+      <c r="Q50" s="19" t="n"/>
+      <c r="R50" s="19" t="n"/>
+      <c r="S50" s="19" t="n"/>
+      <c r="T50" s="19" t="n"/>
+      <c r="U50" s="22" t="n">
         <v>147.5</v>
       </c>
-      <c r="V47" s="22" t="n">
+      <c r="V50" s="22" t="n">
         <v>49.16667</v>
       </c>
-      <c r="W47" s="22" t="n">
+      <c r="W50" s="22" t="n">
         <v>49.16667</v>
       </c>
-      <c r="X47" s="22" t="n">
+      <c r="X50" s="22" t="n">
         <v>49.16667</v>
       </c>
     </row>
-    <row r="48" ht="13" customHeight="1">
-      <c r="A48" s="23" t="inlineStr">
+    <row r="51" ht="13" customHeight="1">
+      <c r="A51" s="23" t="inlineStr">
         <is>
           <t>№ 26-5/090 от 08.09.2026, KGS</t>
         </is>
       </c>
-      <c r="B48" s="24" t="n"/>
-      <c r="C48" s="24" t="n"/>
-      <c r="D48" s="25" t="n"/>
-      <c r="E48" s="26" t="n">
+      <c r="B51" s="24" t="n"/>
+      <c r="C51" s="24" t="n"/>
+      <c r="D51" s="25" t="n"/>
+      <c r="E51" s="26" t="n">
         <v>147.5</v>
       </c>
-      <c r="F48" s="26" t="n">
+      <c r="F51" s="26" t="n">
         <v>125</v>
       </c>
-      <c r="G48" s="26" t="n">
+      <c r="G51" s="26" t="n">
         <v>22.5</v>
       </c>
-      <c r="H48" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="24" t="n"/>
-      <c r="J48" s="24" t="n"/>
-      <c r="K48" s="24" t="n"/>
-      <c r="L48" s="24" t="n"/>
-      <c r="M48" s="24" t="n"/>
-      <c r="N48" s="24" t="n"/>
-      <c r="O48" s="24" t="n"/>
-      <c r="P48" s="24" t="n"/>
-      <c r="Q48" s="24" t="n"/>
-      <c r="R48" s="24" t="n"/>
-      <c r="S48" s="24" t="n"/>
-      <c r="T48" s="24" t="n"/>
-      <c r="U48" s="26" t="n">
+      <c r="H51" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="24" t="n"/>
+      <c r="J51" s="24" t="n"/>
+      <c r="K51" s="24" t="n"/>
+      <c r="L51" s="24" t="n"/>
+      <c r="M51" s="24" t="n"/>
+      <c r="N51" s="24" t="n"/>
+      <c r="O51" s="24" t="n"/>
+      <c r="P51" s="24" t="n"/>
+      <c r="Q51" s="24" t="n"/>
+      <c r="R51" s="24" t="n"/>
+      <c r="S51" s="24" t="n"/>
+      <c r="T51" s="24" t="n"/>
+      <c r="U51" s="26" t="n">
         <v>147.5</v>
       </c>
-      <c r="V48" s="26" t="n">
+      <c r="V51" s="26" t="n">
         <v>49.16667</v>
       </c>
-      <c r="W48" s="26" t="n">
+      <c r="W51" s="26" t="n">
         <v>49.16667</v>
       </c>
-      <c r="X48" s="26" t="n">
+      <c r="X51" s="26" t="n">
         <v>49.16667</v>
       </c>
     </row>
-    <row r="49" ht="13" customHeight="1">
-      <c r="A49" s="18" t="inlineStr">
+    <row r="52" ht="13" customHeight="1">
+      <c r="A52" s="18" t="inlineStr">
         <is>
           <t>ОсОО «Каракол-Сервис»</t>
         </is>
       </c>
-      <c r="B49" s="19" t="n"/>
-      <c r="C49" s="20" t="n">
+      <c r="B52" s="19" t="n"/>
+      <c r="C52" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D49" s="21" t="n"/>
-      <c r="E49" s="19" t="n"/>
-      <c r="F49" s="19" t="n"/>
-      <c r="G49" s="19" t="n"/>
-      <c r="H49" s="19" t="n"/>
-      <c r="I49" s="19" t="n"/>
-      <c r="J49" s="19" t="n"/>
-      <c r="K49" s="19" t="n"/>
-      <c r="L49" s="19" t="n"/>
-      <c r="M49" s="19" t="n"/>
-      <c r="N49" s="19" t="n"/>
-      <c r="O49" s="19" t="n"/>
-      <c r="P49" s="19" t="n"/>
-      <c r="Q49" s="19" t="n"/>
-      <c r="R49" s="19" t="n"/>
-      <c r="S49" s="19" t="n"/>
-      <c r="T49" s="19" t="n"/>
-      <c r="U49" s="19" t="n"/>
-      <c r="V49" s="19" t="n"/>
-      <c r="W49" s="19" t="n"/>
-      <c r="X49" s="19" t="n"/>
-    </row>
-    <row r="50" ht="13" customHeight="1">
-      <c r="A50" s="23" t="inlineStr">
+      <c r="D52" s="21" t="n"/>
+      <c r="E52" s="19" t="n"/>
+      <c r="F52" s="19" t="n"/>
+      <c r="G52" s="19" t="n"/>
+      <c r="H52" s="19" t="n"/>
+      <c r="I52" s="19" t="n"/>
+      <c r="J52" s="19" t="n"/>
+      <c r="K52" s="19" t="n"/>
+      <c r="L52" s="19" t="n"/>
+      <c r="M52" s="19" t="n"/>
+      <c r="N52" s="19" t="n"/>
+      <c r="O52" s="19" t="n"/>
+      <c r="P52" s="19" t="n"/>
+      <c r="Q52" s="19" t="n"/>
+      <c r="R52" s="19" t="n"/>
+      <c r="S52" s="19" t="n"/>
+      <c r="T52" s="19" t="n"/>
+      <c r="U52" s="19" t="n"/>
+      <c r="V52" s="19" t="n"/>
+      <c r="W52" s="19" t="n"/>
+      <c r="X52" s="19" t="n"/>
+    </row>
+    <row r="53" ht="13" customHeight="1">
+      <c r="A53" s="23" t="inlineStr">
         <is>
           <t>№ 25-3/014 от 05.03.2025, KGS</t>
         </is>
       </c>
-      <c r="B50" s="24" t="n"/>
-      <c r="C50" s="24" t="n"/>
-      <c r="D50" s="25" t="n"/>
-      <c r="E50" s="24" t="n"/>
-      <c r="F50" s="24" t="n"/>
-      <c r="G50" s="24" t="n"/>
-      <c r="H50" s="24" t="n"/>
-      <c r="I50" s="24" t="n"/>
-      <c r="J50" s="24" t="n"/>
-      <c r="K50" s="24" t="n"/>
-      <c r="L50" s="24" t="n"/>
-      <c r="M50" s="24" t="n"/>
-      <c r="N50" s="24" t="n"/>
-      <c r="O50" s="24" t="n"/>
-      <c r="P50" s="24" t="n"/>
-      <c r="Q50" s="24" t="n"/>
-      <c r="R50" s="24" t="n"/>
-      <c r="S50" s="24" t="n"/>
-      <c r="T50" s="24" t="n"/>
-      <c r="U50" s="24" t="n"/>
-      <c r="V50" s="24" t="n"/>
-      <c r="W50" s="24" t="n"/>
-      <c r="X50" s="24" t="n"/>
-    </row>
-    <row r="51" ht="13" customHeight="1">
-      <c r="A51" s="18" t="inlineStr">
-        <is>
-          <t>ОсОО «Ысык-Көл Логистик»</t>
-        </is>
-      </c>
-      <c r="B51" s="19" t="n"/>
-      <c r="C51" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D51" s="21" t="n"/>
-      <c r="E51" s="22" t="n">
-        <v>877.5</v>
-      </c>
-      <c r="F51" s="22" t="n">
-        <v>600</v>
-      </c>
-      <c r="G51" s="22" t="n">
-        <v>277.5</v>
-      </c>
-      <c r="H51" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="22" t="n">
-        <v>225</v>
-      </c>
-      <c r="J51" s="22" t="n">
-        <v>75.41667</v>
-      </c>
-      <c r="K51" s="22" t="n">
-        <v>75</v>
-      </c>
-      <c r="L51" s="22" t="n">
-        <v>74.58333</v>
-      </c>
-      <c r="M51" s="22" t="n">
-        <v>221.25</v>
-      </c>
-      <c r="N51" s="22" t="n">
-        <v>74.16667</v>
-      </c>
-      <c r="O51" s="22" t="n">
-        <v>73.75</v>
-      </c>
-      <c r="P51" s="22" t="n">
-        <v>73.33333</v>
-      </c>
-      <c r="Q51" s="22" t="n">
-        <v>217.5</v>
-      </c>
-      <c r="R51" s="22" t="n">
-        <v>72.91667</v>
-      </c>
-      <c r="S51" s="22" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="T51" s="22" t="n">
-        <v>72.08333</v>
-      </c>
-      <c r="U51" s="22" t="n">
-        <v>213.75</v>
-      </c>
-      <c r="V51" s="22" t="n">
-        <v>71.66667</v>
-      </c>
-      <c r="W51" s="22" t="n">
-        <v>71.25</v>
-      </c>
-      <c r="X51" s="22" t="n">
-        <v>70.83333</v>
-      </c>
-    </row>
-    <row r="52" ht="13" customHeight="1">
-      <c r="A52" s="23" t="inlineStr">
-        <is>
-          <t>№ 21-6/144 от 02.06.2021, KGS</t>
-        </is>
-      </c>
-      <c r="B52" s="24" t="n"/>
-      <c r="C52" s="24" t="n"/>
-      <c r="D52" s="25" t="n"/>
-      <c r="E52" s="26" t="n">
-        <v>877.5</v>
-      </c>
-      <c r="F52" s="26" t="n">
-        <v>600</v>
-      </c>
-      <c r="G52" s="26" t="n">
-        <v>277.5</v>
-      </c>
-      <c r="H52" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="26" t="n">
-        <v>225</v>
-      </c>
-      <c r="J52" s="26" t="n">
-        <v>75.41667</v>
-      </c>
-      <c r="K52" s="26" t="n">
-        <v>75</v>
-      </c>
-      <c r="L52" s="26" t="n">
-        <v>74.58333</v>
-      </c>
-      <c r="M52" s="26" t="n">
-        <v>221.25</v>
-      </c>
-      <c r="N52" s="26" t="n">
-        <v>74.16667</v>
-      </c>
-      <c r="O52" s="26" t="n">
-        <v>73.75</v>
-      </c>
-      <c r="P52" s="26" t="n">
-        <v>73.33333</v>
-      </c>
-      <c r="Q52" s="26" t="n">
-        <v>217.5</v>
-      </c>
-      <c r="R52" s="26" t="n">
-        <v>72.91667</v>
-      </c>
-      <c r="S52" s="26" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="T52" s="26" t="n">
-        <v>72.08333</v>
-      </c>
-      <c r="U52" s="26" t="n">
-        <v>213.75</v>
-      </c>
-      <c r="V52" s="26" t="n">
-        <v>71.66667</v>
-      </c>
-      <c r="W52" s="26" t="n">
-        <v>71.25</v>
-      </c>
-      <c r="X52" s="26" t="n">
-        <v>70.83333</v>
-      </c>
-    </row>
-    <row r="53" ht="13" customHeight="1">
-      <c r="A53" s="14" t="inlineStr">
-        <is>
-          <t>Группа 1.2 — с отставанием от графика</t>
-        </is>
-      </c>
-      <c r="B53" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="C53" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="D53" s="16" t="n"/>
-      <c r="E53" s="17" t="n">
-        <v>1538.67143</v>
-      </c>
-      <c r="F53" s="17" t="n">
-        <v>1276.57143</v>
-      </c>
-      <c r="G53" s="17" t="n">
-        <v>243.7</v>
-      </c>
-      <c r="H53" s="17" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="I53" s="17" t="n">
-        <v>451.39286</v>
-      </c>
-      <c r="J53" s="17" t="n">
-        <v>150.49762</v>
-      </c>
-      <c r="K53" s="17" t="n">
-        <v>150.46429</v>
-      </c>
-      <c r="L53" s="17" t="n">
-        <v>150.43096</v>
-      </c>
-      <c r="M53" s="17" t="n">
-        <v>410.59286</v>
-      </c>
-      <c r="N53" s="17" t="n">
-        <v>150.39762</v>
-      </c>
-      <c r="O53" s="17" t="n">
-        <v>150.36429</v>
-      </c>
-      <c r="P53" s="17" t="n">
-        <v>109.83096</v>
-      </c>
-      <c r="Q53" s="17" t="n">
-        <v>347.69286</v>
-      </c>
-      <c r="R53" s="17" t="n">
-        <v>109.79762</v>
-      </c>
-      <c r="S53" s="17" t="n">
-        <v>109.76429</v>
-      </c>
-      <c r="T53" s="17" t="n">
-        <v>128.13096</v>
-      </c>
-      <c r="U53" s="17" t="n">
-        <v>328.99286</v>
-      </c>
-      <c r="V53" s="17" t="n">
-        <v>109.69762</v>
-      </c>
-      <c r="W53" s="17" t="n">
-        <v>109.66429</v>
-      </c>
-      <c r="X53" s="17" t="n">
-        <v>109.63096</v>
-      </c>
+      <c r="B53" s="24" t="n"/>
+      <c r="C53" s="24" t="n"/>
+      <c r="D53" s="25" t="n"/>
+      <c r="E53" s="24" t="n"/>
+      <c r="F53" s="24" t="n"/>
+      <c r="G53" s="24" t="n"/>
+      <c r="H53" s="24" t="n"/>
+      <c r="I53" s="24" t="n"/>
+      <c r="J53" s="24" t="n"/>
+      <c r="K53" s="24" t="n"/>
+      <c r="L53" s="24" t="n"/>
+      <c r="M53" s="24" t="n"/>
+      <c r="N53" s="24" t="n"/>
+      <c r="O53" s="24" t="n"/>
+      <c r="P53" s="24" t="n"/>
+      <c r="Q53" s="24" t="n"/>
+      <c r="R53" s="24" t="n"/>
+      <c r="S53" s="24" t="n"/>
+      <c r="T53" s="24" t="n"/>
+      <c r="U53" s="24" t="n"/>
+      <c r="V53" s="24" t="n"/>
+      <c r="W53" s="24" t="n"/>
+      <c r="X53" s="24" t="n"/>
     </row>
     <row r="54" ht="13" customHeight="1">
       <c r="A54" s="18" t="inlineStr">
         <is>
-          <t>КФХ «Ак-Суу»</t>
+          <t>ОсОО «Ысык-Көл Логистик»</t>
         </is>
       </c>
       <c r="B54" s="19" t="n"/>
@@ -4017,472 +4013,472 @@
       </c>
       <c r="D54" s="21" t="n"/>
       <c r="E54" s="22" t="n">
-        <v>220.9</v>
+        <v>877.5</v>
       </c>
       <c r="F54" s="22" t="n">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="G54" s="22" t="n">
-        <v>2.5</v>
+        <v>277.5</v>
       </c>
       <c r="H54" s="22" t="n">
-        <v>18.4</v>
+        <v>0</v>
       </c>
       <c r="I54" s="22" t="n">
-        <v>121.5</v>
+        <v>225</v>
       </c>
       <c r="J54" s="22" t="n">
-        <v>40.5</v>
+        <v>75.41667</v>
       </c>
       <c r="K54" s="22" t="n">
-        <v>40.5</v>
+        <v>75</v>
       </c>
       <c r="L54" s="22" t="n">
-        <v>40.5</v>
+        <v>74.58333</v>
       </c>
       <c r="M54" s="22" t="n">
-        <v>81</v>
+        <v>221.25</v>
       </c>
       <c r="N54" s="22" t="n">
-        <v>40.5</v>
+        <v>74.16667</v>
       </c>
       <c r="O54" s="22" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="P54" s="19" t="n"/>
+        <v>73.75</v>
+      </c>
+      <c r="P54" s="22" t="n">
+        <v>73.33333</v>
+      </c>
       <c r="Q54" s="22" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="R54" s="19" t="n"/>
-      <c r="S54" s="19" t="n"/>
+        <v>217.5</v>
+      </c>
+      <c r="R54" s="22" t="n">
+        <v>72.91667</v>
+      </c>
+      <c r="S54" s="22" t="n">
+        <v>72.5</v>
+      </c>
       <c r="T54" s="22" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="U54" s="19" t="n"/>
-      <c r="V54" s="19" t="n"/>
-      <c r="W54" s="19" t="n"/>
-      <c r="X54" s="19" t="n"/>
+        <v>72.08333</v>
+      </c>
+      <c r="U54" s="22" t="n">
+        <v>213.75</v>
+      </c>
+      <c r="V54" s="22" t="n">
+        <v>71.66667</v>
+      </c>
+      <c r="W54" s="22" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="X54" s="22" t="n">
+        <v>70.83333</v>
+      </c>
     </row>
     <row r="55" ht="13" customHeight="1">
       <c r="A55" s="23" t="inlineStr">
         <is>
-          <t>№ 20-6/027 от 12.05.2020, KGS</t>
+          <t>№ 21-6/144 от 02.06.2021, KGS</t>
         </is>
       </c>
       <c r="B55" s="24" t="n"/>
       <c r="C55" s="24" t="n"/>
-      <c r="D55" s="31" t="n">
+      <c r="D55" s="25" t="n"/>
+      <c r="E55" s="26" t="n">
+        <v>877.5</v>
+      </c>
+      <c r="F55" s="26" t="n">
+        <v>600</v>
+      </c>
+      <c r="G55" s="26" t="n">
+        <v>277.5</v>
+      </c>
+      <c r="H55" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="26" t="n">
+        <v>225</v>
+      </c>
+      <c r="J55" s="26" t="n">
+        <v>75.41667</v>
+      </c>
+      <c r="K55" s="26" t="n">
+        <v>75</v>
+      </c>
+      <c r="L55" s="26" t="n">
+        <v>74.58333</v>
+      </c>
+      <c r="M55" s="26" t="n">
+        <v>221.25</v>
+      </c>
+      <c r="N55" s="26" t="n">
+        <v>74.16667</v>
+      </c>
+      <c r="O55" s="26" t="n">
+        <v>73.75</v>
+      </c>
+      <c r="P55" s="26" t="n">
+        <v>73.33333</v>
+      </c>
+      <c r="Q55" s="26" t="n">
+        <v>217.5</v>
+      </c>
+      <c r="R55" s="26" t="n">
+        <v>72.91667</v>
+      </c>
+      <c r="S55" s="26" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="T55" s="26" t="n">
+        <v>72.08333</v>
+      </c>
+      <c r="U55" s="26" t="n">
+        <v>213.75</v>
+      </c>
+      <c r="V55" s="26" t="n">
+        <v>71.66667</v>
+      </c>
+      <c r="W55" s="26" t="n">
+        <v>71.25</v>
+      </c>
+      <c r="X55" s="26" t="n">
+        <v>70.83333</v>
+      </c>
+    </row>
+    <row r="56" ht="13" customHeight="1">
+      <c r="A56" s="14" t="inlineStr">
+        <is>
+          <t>Группа 1.2 — с отставанием от графика</t>
+        </is>
+      </c>
+      <c r="B56" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C56" s="15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D56" s="16" t="n"/>
+      <c r="E56" s="17" t="n">
+        <v>1538.67143</v>
+      </c>
+      <c r="F56" s="17" t="n">
+        <v>1276.57143</v>
+      </c>
+      <c r="G56" s="17" t="n">
+        <v>243.7</v>
+      </c>
+      <c r="H56" s="17" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="I56" s="17" t="n">
+        <v>451.39286</v>
+      </c>
+      <c r="J56" s="17" t="n">
+        <v>150.49762</v>
+      </c>
+      <c r="K56" s="17" t="n">
+        <v>150.46429</v>
+      </c>
+      <c r="L56" s="17" t="n">
+        <v>150.43096</v>
+      </c>
+      <c r="M56" s="17" t="n">
+        <v>410.59286</v>
+      </c>
+      <c r="N56" s="17" t="n">
+        <v>150.39762</v>
+      </c>
+      <c r="O56" s="17" t="n">
+        <v>150.36429</v>
+      </c>
+      <c r="P56" s="17" t="n">
+        <v>109.83096</v>
+      </c>
+      <c r="Q56" s="17" t="n">
+        <v>347.69286</v>
+      </c>
+      <c r="R56" s="17" t="n">
+        <v>109.79762</v>
+      </c>
+      <c r="S56" s="17" t="n">
+        <v>109.76429</v>
+      </c>
+      <c r="T56" s="17" t="n">
+        <v>128.13096</v>
+      </c>
+      <c r="U56" s="17" t="n">
+        <v>328.99286</v>
+      </c>
+      <c r="V56" s="17" t="n">
+        <v>109.69762</v>
+      </c>
+      <c r="W56" s="17" t="n">
+        <v>109.66429</v>
+      </c>
+      <c r="X56" s="17" t="n">
+        <v>109.63096</v>
+      </c>
+    </row>
+    <row r="57" ht="13" customHeight="1">
+      <c r="A57" s="18" t="inlineStr">
+        <is>
+          <t>КФХ «Ак-Суу»</t>
+        </is>
+      </c>
+      <c r="B57" s="19" t="n"/>
+      <c r="C57" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D57" s="21" t="n"/>
+      <c r="E57" s="22" t="n">
+        <v>220.9</v>
+      </c>
+      <c r="F57" s="22" t="n">
+        <v>200</v>
+      </c>
+      <c r="G57" s="22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H57" s="22" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="I57" s="22" t="n">
+        <v>121.5</v>
+      </c>
+      <c r="J57" s="22" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="K57" s="22" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="L57" s="22" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="M57" s="22" t="n">
+        <v>81</v>
+      </c>
+      <c r="N57" s="22" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="O57" s="22" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="P57" s="19" t="n"/>
+      <c r="Q57" s="22" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="R57" s="19" t="n"/>
+      <c r="S57" s="19" t="n"/>
+      <c r="T57" s="22" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="U57" s="19" t="n"/>
+      <c r="V57" s="19" t="n"/>
+      <c r="W57" s="19" t="n"/>
+      <c r="X57" s="19" t="n"/>
+    </row>
+    <row r="58" ht="13" customHeight="1">
+      <c r="A58" s="23" t="inlineStr">
+        <is>
+          <t>№ 20-6/027 от 12.05.2020, KGS</t>
+        </is>
+      </c>
+      <c r="B58" s="24" t="n"/>
+      <c r="C58" s="24" t="n"/>
+      <c r="D58" s="31" t="n">
         <v>46254</v>
       </c>
-      <c r="E55" s="26" t="n">
+      <c r="E58" s="26" t="n">
         <v>220.9</v>
       </c>
-      <c r="F55" s="26" t="n">
+      <c r="F58" s="26" t="n">
         <v>200</v>
       </c>
-      <c r="G55" s="26" t="n">
+      <c r="G58" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="H55" s="26" t="n">
+      <c r="H58" s="26" t="n">
         <v>18.4</v>
       </c>
-      <c r="I55" s="26" t="n">
+      <c r="I58" s="26" t="n">
         <v>121.5</v>
       </c>
-      <c r="J55" s="26" t="n">
+      <c r="J58" s="26" t="n">
         <v>40.5</v>
       </c>
-      <c r="K55" s="26" t="n">
+      <c r="K58" s="26" t="n">
         <v>40.5</v>
       </c>
-      <c r="L55" s="26" t="n">
+      <c r="L58" s="26" t="n">
         <v>40.5</v>
       </c>
-      <c r="M55" s="26" t="n">
+      <c r="M58" s="26" t="n">
         <v>81</v>
       </c>
-      <c r="N55" s="26" t="n">
+      <c r="N58" s="26" t="n">
         <v>40.5</v>
       </c>
-      <c r="O55" s="26" t="n">
+      <c r="O58" s="26" t="n">
         <v>40.5</v>
       </c>
-      <c r="P55" s="24" t="n"/>
-      <c r="Q55" s="26" t="n">
+      <c r="P58" s="24" t="n"/>
+      <c r="Q58" s="26" t="n">
         <v>18.4</v>
       </c>
-      <c r="R55" s="24" t="n"/>
-      <c r="S55" s="24" t="n"/>
-      <c r="T55" s="26" t="n">
+      <c r="R58" s="24" t="n"/>
+      <c r="S58" s="24" t="n"/>
+      <c r="T58" s="26" t="n">
         <v>18.4</v>
       </c>
-      <c r="U55" s="24" t="n"/>
-      <c r="V55" s="24" t="n"/>
-      <c r="W55" s="24" t="n"/>
-      <c r="X55" s="24" t="n"/>
-    </row>
-    <row r="56" ht="13" customHeight="1">
-      <c r="A56" s="18" t="inlineStr">
+      <c r="U58" s="24" t="n"/>
+      <c r="V58" s="24" t="n"/>
+      <c r="W58" s="24" t="n"/>
+      <c r="X58" s="24" t="n"/>
+    </row>
+    <row r="59" ht="13" customHeight="1">
+      <c r="A59" s="18" t="inlineStr">
         <is>
           <t>Иманалиев Бакыт Тологонович</t>
         </is>
       </c>
-      <c r="B56" s="19" t="n"/>
-      <c r="C56" s="20" t="n">
+      <c r="B59" s="19" t="n"/>
+      <c r="C59" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="D56" s="21" t="n"/>
-      <c r="E56" s="22" t="n">
+      <c r="D59" s="21" t="n"/>
+      <c r="E59" s="22" t="n">
         <v>64.2</v>
       </c>
-      <c r="F56" s="22" t="n">
+      <c r="F59" s="22" t="n">
         <v>48</v>
       </c>
-      <c r="G56" s="22" t="n">
+      <c r="G59" s="22" t="n">
         <v>16.2</v>
       </c>
-      <c r="H56" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="22" t="n">
+      <c r="H59" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="22" t="n">
         <v>16.5</v>
       </c>
-      <c r="J56" s="22" t="n">
+      <c r="J59" s="22" t="n">
         <v>5.53333</v>
       </c>
-      <c r="K56" s="22" t="n">
+      <c r="K59" s="22" t="n">
         <v>5.5</v>
       </c>
-      <c r="L56" s="22" t="n">
+      <c r="L59" s="22" t="n">
         <v>5.46667</v>
       </c>
-      <c r="M56" s="22" t="n">
+      <c r="M59" s="22" t="n">
         <v>16.2</v>
       </c>
-      <c r="N56" s="22" t="n">
+      <c r="N59" s="22" t="n">
         <v>5.43333</v>
       </c>
-      <c r="O56" s="22" t="n">
+      <c r="O59" s="22" t="n">
         <v>5.4</v>
       </c>
-      <c r="P56" s="22" t="n">
+      <c r="P59" s="22" t="n">
         <v>5.36667</v>
       </c>
-      <c r="Q56" s="22" t="n">
+      <c r="Q59" s="22" t="n">
         <v>15.9</v>
       </c>
-      <c r="R56" s="22" t="n">
+      <c r="R59" s="22" t="n">
         <v>5.33333</v>
       </c>
-      <c r="S56" s="22" t="n">
+      <c r="S59" s="22" t="n">
         <v>5.3</v>
       </c>
-      <c r="T56" s="22" t="n">
+      <c r="T59" s="22" t="n">
         <v>5.26667</v>
       </c>
-      <c r="U56" s="22" t="n">
+      <c r="U59" s="22" t="n">
         <v>15.6</v>
       </c>
-      <c r="V56" s="22" t="n">
+      <c r="V59" s="22" t="n">
         <v>5.23333</v>
       </c>
-      <c r="W56" s="22" t="n">
+      <c r="W59" s="22" t="n">
         <v>5.2</v>
       </c>
-      <c r="X56" s="22" t="n">
+      <c r="X59" s="22" t="n">
         <v>5.16667</v>
       </c>
     </row>
-    <row r="57" ht="13" customHeight="1">
-      <c r="A57" s="23" t="inlineStr">
+    <row r="60" ht="13" customHeight="1">
+      <c r="A60" s="23" t="inlineStr">
         <is>
           <t>№ 24-2/077 от 14.05.2024, KGS</t>
         </is>
       </c>
-      <c r="B57" s="24" t="n"/>
-      <c r="C57" s="24" t="n"/>
-      <c r="D57" s="25" t="n"/>
-      <c r="E57" s="26" t="n">
+      <c r="B60" s="24" t="n"/>
+      <c r="C60" s="24" t="n"/>
+      <c r="D60" s="25" t="n"/>
+      <c r="E60" s="26" t="n">
         <v>64.2</v>
       </c>
-      <c r="F57" s="26" t="n">
+      <c r="F60" s="26" t="n">
         <v>48</v>
       </c>
-      <c r="G57" s="26" t="n">
+      <c r="G60" s="26" t="n">
         <v>16.2</v>
       </c>
-      <c r="H57" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="26" t="n">
+      <c r="H60" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="26" t="n">
         <v>16.5</v>
       </c>
-      <c r="J57" s="26" t="n">
+      <c r="J60" s="26" t="n">
         <v>5.53333</v>
       </c>
-      <c r="K57" s="26" t="n">
+      <c r="K60" s="26" t="n">
         <v>5.5</v>
       </c>
-      <c r="L57" s="26" t="n">
+      <c r="L60" s="26" t="n">
         <v>5.46667</v>
       </c>
-      <c r="M57" s="26" t="n">
+      <c r="M60" s="26" t="n">
         <v>16.2</v>
       </c>
-      <c r="N57" s="26" t="n">
+      <c r="N60" s="26" t="n">
         <v>5.43333</v>
       </c>
-      <c r="O57" s="26" t="n">
+      <c r="O60" s="26" t="n">
         <v>5.4</v>
       </c>
-      <c r="P57" s="26" t="n">
+      <c r="P60" s="26" t="n">
         <v>5.36667</v>
       </c>
-      <c r="Q57" s="26" t="n">
+      <c r="Q60" s="26" t="n">
         <v>15.9</v>
       </c>
-      <c r="R57" s="26" t="n">
+      <c r="R60" s="26" t="n">
         <v>5.33333</v>
       </c>
-      <c r="S57" s="26" t="n">
+      <c r="S60" s="26" t="n">
         <v>5.3</v>
       </c>
-      <c r="T57" s="26" t="n">
+      <c r="T60" s="26" t="n">
         <v>5.26667</v>
       </c>
-      <c r="U57" s="26" t="n">
+      <c r="U60" s="26" t="n">
         <v>15.6</v>
       </c>
-      <c r="V57" s="26" t="n">
+      <c r="V60" s="26" t="n">
         <v>5.23333</v>
       </c>
-      <c r="W57" s="26" t="n">
+      <c r="W60" s="26" t="n">
         <v>5.2</v>
       </c>
-      <c r="X57" s="26" t="n">
+      <c r="X60" s="26" t="n">
         <v>5.16667</v>
-      </c>
-    </row>
-    <row r="58" ht="13" customHeight="1">
-      <c r="A58" s="18" t="inlineStr">
-        <is>
-          <t>ОсОО «Ош-Текстиль»</t>
-        </is>
-      </c>
-      <c r="B58" s="19" t="n"/>
-      <c r="C58" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D58" s="21" t="n"/>
-      <c r="E58" s="22" t="n">
-        <v>1253.57143</v>
-      </c>
-      <c r="F58" s="22" t="n">
-        <v>1028.57143</v>
-      </c>
-      <c r="G58" s="22" t="n">
-        <v>225</v>
-      </c>
-      <c r="H58" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="22" t="n">
-        <v>313.39286</v>
-      </c>
-      <c r="J58" s="22" t="n">
-        <v>104.46429</v>
-      </c>
-      <c r="K58" s="22" t="n">
-        <v>104.46429</v>
-      </c>
-      <c r="L58" s="22" t="n">
-        <v>104.46429</v>
-      </c>
-      <c r="M58" s="22" t="n">
-        <v>313.39286</v>
-      </c>
-      <c r="N58" s="22" t="n">
-        <v>104.46429</v>
-      </c>
-      <c r="O58" s="22" t="n">
-        <v>104.46429</v>
-      </c>
-      <c r="P58" s="22" t="n">
-        <v>104.46429</v>
-      </c>
-      <c r="Q58" s="22" t="n">
-        <v>313.39286</v>
-      </c>
-      <c r="R58" s="22" t="n">
-        <v>104.46429</v>
-      </c>
-      <c r="S58" s="22" t="n">
-        <v>104.46429</v>
-      </c>
-      <c r="T58" s="22" t="n">
-        <v>104.46429</v>
-      </c>
-      <c r="U58" s="22" t="n">
-        <v>313.39286</v>
-      </c>
-      <c r="V58" s="22" t="n">
-        <v>104.46429</v>
-      </c>
-      <c r="W58" s="22" t="n">
-        <v>104.46429</v>
-      </c>
-      <c r="X58" s="22" t="n">
-        <v>104.46429</v>
-      </c>
-    </row>
-    <row r="59" ht="13" customHeight="1">
-      <c r="A59" s="23" t="inlineStr">
-        <is>
-          <t>№ 21-5/203 от 09.09.2021, KGS</t>
-        </is>
-      </c>
-      <c r="B59" s="24" t="n"/>
-      <c r="C59" s="24" t="n"/>
-      <c r="D59" s="25" t="n"/>
-      <c r="E59" s="26" t="n">
-        <v>1253.57143</v>
-      </c>
-      <c r="F59" s="26" t="n">
-        <v>1028.57143</v>
-      </c>
-      <c r="G59" s="26" t="n">
-        <v>225</v>
-      </c>
-      <c r="H59" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="26" t="n">
-        <v>313.39286</v>
-      </c>
-      <c r="J59" s="26" t="n">
-        <v>104.46429</v>
-      </c>
-      <c r="K59" s="26" t="n">
-        <v>104.46429</v>
-      </c>
-      <c r="L59" s="26" t="n">
-        <v>104.46429</v>
-      </c>
-      <c r="M59" s="26" t="n">
-        <v>313.39286</v>
-      </c>
-      <c r="N59" s="26" t="n">
-        <v>104.46429</v>
-      </c>
-      <c r="O59" s="26" t="n">
-        <v>104.46429</v>
-      </c>
-      <c r="P59" s="26" t="n">
-        <v>104.46429</v>
-      </c>
-      <c r="Q59" s="26" t="n">
-        <v>313.39286</v>
-      </c>
-      <c r="R59" s="26" t="n">
-        <v>104.46429</v>
-      </c>
-      <c r="S59" s="26" t="n">
-        <v>104.46429</v>
-      </c>
-      <c r="T59" s="26" t="n">
-        <v>104.46429</v>
-      </c>
-      <c r="U59" s="26" t="n">
-        <v>313.39286</v>
-      </c>
-      <c r="V59" s="26" t="n">
-        <v>104.46429</v>
-      </c>
-      <c r="W59" s="26" t="n">
-        <v>104.46429</v>
-      </c>
-      <c r="X59" s="26" t="n">
-        <v>104.46429</v>
-      </c>
-    </row>
-    <row r="60" ht="13" customHeight="1">
-      <c r="A60" s="14" t="inlineStr">
-        <is>
-          <t>Группа 2.1 — работа с судебными органами</t>
-        </is>
-      </c>
-      <c r="B60" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C60" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" s="16" t="n"/>
-      <c r="E60" s="17" t="n">
-        <v>1212.15</v>
-      </c>
-      <c r="F60" s="17" t="n">
-        <v>1050</v>
-      </c>
-      <c r="G60" s="17" t="n">
-        <v>129.99999</v>
-      </c>
-      <c r="H60" s="17" t="n">
-        <v>32.15001</v>
-      </c>
-      <c r="I60" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P60" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S60" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" s="17" t="n">
-        <v>1212.15</v>
-      </c>
-      <c r="V60" s="17" t="n">
-        <v>404.05</v>
-      </c>
-      <c r="W60" s="17" t="n">
-        <v>404.05</v>
-      </c>
-      <c r="X60" s="17" t="n">
-        <v>404.05</v>
       </c>
     </row>
     <row r="61" ht="13" customHeight="1">
       <c r="A61" s="18" t="inlineStr">
         <is>
-          <t>ОсОО «Нарын-Агро»</t>
+          <t>ОсОО «Ош-Текстиль»</t>
         </is>
       </c>
       <c r="B61" s="19" t="n"/>
@@ -4491,142 +4487,140 @@
       </c>
       <c r="D61" s="21" t="n"/>
       <c r="E61" s="22" t="n">
-        <v>1212.15</v>
+        <v>1253.57143</v>
       </c>
       <c r="F61" s="22" t="n">
-        <v>1050</v>
+        <v>1028.57143</v>
       </c>
       <c r="G61" s="22" t="n">
-        <v>129.99999</v>
+        <v>225</v>
       </c>
       <c r="H61" s="22" t="n">
-        <v>32.15001</v>
+        <v>0</v>
       </c>
       <c r="I61" s="22" t="n">
-        <v>0</v>
+        <v>313.39286</v>
       </c>
       <c r="J61" s="22" t="n">
-        <v>0</v>
+        <v>104.46429</v>
       </c>
       <c r="K61" s="22" t="n">
-        <v>0</v>
+        <v>104.46429</v>
       </c>
       <c r="L61" s="22" t="n">
-        <v>0</v>
+        <v>104.46429</v>
       </c>
       <c r="M61" s="22" t="n">
-        <v>0</v>
+        <v>313.39286</v>
       </c>
       <c r="N61" s="22" t="n">
-        <v>0</v>
+        <v>104.46429</v>
       </c>
       <c r="O61" s="22" t="n">
-        <v>0</v>
+        <v>104.46429</v>
       </c>
       <c r="P61" s="22" t="n">
-        <v>0</v>
+        <v>104.46429</v>
       </c>
       <c r="Q61" s="22" t="n">
-        <v>0</v>
+        <v>313.39286</v>
       </c>
       <c r="R61" s="22" t="n">
-        <v>0</v>
+        <v>104.46429</v>
       </c>
       <c r="S61" s="22" t="n">
-        <v>0</v>
+        <v>104.46429</v>
       </c>
       <c r="T61" s="22" t="n">
-        <v>0</v>
+        <v>104.46429</v>
       </c>
       <c r="U61" s="22" t="n">
-        <v>1212.15</v>
+        <v>313.39286</v>
       </c>
       <c r="V61" s="22" t="n">
-        <v>404.05</v>
+        <v>104.46429</v>
       </c>
       <c r="W61" s="22" t="n">
-        <v>404.05</v>
+        <v>104.46429</v>
       </c>
       <c r="X61" s="22" t="n">
-        <v>404.05</v>
+        <v>104.46429</v>
       </c>
     </row>
     <row r="62" ht="13" customHeight="1">
       <c r="A62" s="23" t="inlineStr">
         <is>
-          <t>№ 21-2/077 от 18.05.2021, KGS</t>
+          <t>№ 21-5/203 от 09.09.2021, KGS</t>
         </is>
       </c>
       <c r="B62" s="24" t="n"/>
       <c r="C62" s="24" t="n"/>
-      <c r="D62" s="31" t="n">
-        <v>46275</v>
-      </c>
+      <c r="D62" s="25" t="n"/>
       <c r="E62" s="26" t="n">
-        <v>1212.15</v>
+        <v>1253.57143</v>
       </c>
       <c r="F62" s="26" t="n">
-        <v>1050</v>
+        <v>1028.57143</v>
       </c>
       <c r="G62" s="26" t="n">
-        <v>129.99999</v>
+        <v>225</v>
       </c>
       <c r="H62" s="26" t="n">
-        <v>32.15001</v>
+        <v>0</v>
       </c>
       <c r="I62" s="26" t="n">
-        <v>0</v>
+        <v>313.39286</v>
       </c>
       <c r="J62" s="26" t="n">
-        <v>0</v>
+        <v>104.46429</v>
       </c>
       <c r="K62" s="26" t="n">
-        <v>0</v>
+        <v>104.46429</v>
       </c>
       <c r="L62" s="26" t="n">
-        <v>0</v>
+        <v>104.46429</v>
       </c>
       <c r="M62" s="26" t="n">
-        <v>0</v>
+        <v>313.39286</v>
       </c>
       <c r="N62" s="26" t="n">
-        <v>0</v>
+        <v>104.46429</v>
       </c>
       <c r="O62" s="26" t="n">
-        <v>0</v>
+        <v>104.46429</v>
       </c>
       <c r="P62" s="26" t="n">
-        <v>0</v>
+        <v>104.46429</v>
       </c>
       <c r="Q62" s="26" t="n">
-        <v>0</v>
+        <v>313.39286</v>
       </c>
       <c r="R62" s="26" t="n">
-        <v>0</v>
+        <v>104.46429</v>
       </c>
       <c r="S62" s="26" t="n">
-        <v>0</v>
+        <v>104.46429</v>
       </c>
       <c r="T62" s="26" t="n">
-        <v>0</v>
+        <v>104.46429</v>
       </c>
       <c r="U62" s="26" t="n">
-        <v>1212.15</v>
+        <v>313.39286</v>
       </c>
       <c r="V62" s="26" t="n">
-        <v>404.05</v>
+        <v>104.46429</v>
       </c>
       <c r="W62" s="26" t="n">
-        <v>404.05</v>
+        <v>104.46429</v>
       </c>
       <c r="X62" s="26" t="n">
-        <v>404.05</v>
+        <v>104.46429</v>
       </c>
     </row>
     <row r="63" ht="13" customHeight="1">
       <c r="A63" s="14" t="inlineStr">
         <is>
-          <t>Группа 2.2 — работа по исполнительным листам</t>
+          <t>Группа 2.1 — работа с судебными органами</t>
         </is>
       </c>
       <c r="B63" s="15" t="n">
@@ -4914,7 +4908,7 @@
     <row r="67" ht="13" customHeight="1">
       <c r="A67" s="14" t="inlineStr">
         <is>
-          <t>Группа 2.3 — инициирование банкротства</t>
+          <t>Группа 2.2 — работа по исполнительным листам</t>
         </is>
       </c>
       <c r="B67" s="15" t="n">
@@ -4925,16 +4919,16 @@
       </c>
       <c r="D67" s="16" t="n"/>
       <c r="E67" s="17" t="n">
-        <v>0</v>
+        <v>1212.15</v>
       </c>
       <c r="F67" s="17" t="n">
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="G67" s="17" t="n">
-        <v>0</v>
+        <v>129.99999</v>
       </c>
       <c r="H67" s="17" t="n">
-        <v>0</v>
+        <v>32.15001</v>
       </c>
       <c r="I67" s="17" t="n">
         <v>0</v>
@@ -4973,22 +4967,22 @@
         <v>0</v>
       </c>
       <c r="U67" s="17" t="n">
-        <v>0</v>
+        <v>1212.15</v>
       </c>
       <c r="V67" s="17" t="n">
-        <v>0</v>
+        <v>404.05</v>
       </c>
       <c r="W67" s="17" t="n">
-        <v>0</v>
+        <v>404.05</v>
       </c>
       <c r="X67" s="17" t="n">
-        <v>0</v>
+        <v>404.05</v>
       </c>
     </row>
     <row r="68" ht="13" customHeight="1">
       <c r="A68" s="18" t="inlineStr">
         <is>
-          <t>ОсОО «Талас-Бал»</t>
+          <t>ОсОО «Нарын-Агро»</t>
         </is>
       </c>
       <c r="B68" s="19" t="n"/>
@@ -4997,16 +4991,16 @@
       </c>
       <c r="D68" s="21" t="n"/>
       <c r="E68" s="22" t="n">
-        <v>0</v>
+        <v>1212.15</v>
       </c>
       <c r="F68" s="22" t="n">
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="G68" s="22" t="n">
-        <v>0</v>
+        <v>129.99999</v>
       </c>
       <c r="H68" s="22" t="n">
-        <v>0</v>
+        <v>32.15001</v>
       </c>
       <c r="I68" s="22" t="n">
         <v>0</v>
@@ -5045,38 +5039,40 @@
         <v>0</v>
       </c>
       <c r="U68" s="22" t="n">
-        <v>0</v>
+        <v>1212.15</v>
       </c>
       <c r="V68" s="22" t="n">
-        <v>0</v>
+        <v>404.05</v>
       </c>
       <c r="W68" s="22" t="n">
-        <v>0</v>
+        <v>404.05</v>
       </c>
       <c r="X68" s="22" t="n">
-        <v>0</v>
+        <v>404.05</v>
       </c>
     </row>
     <row r="69" ht="13" customHeight="1">
       <c r="A69" s="23" t="inlineStr">
         <is>
-          <t>№ 23-4/021 от 21.08.2023, KGS</t>
+          <t>№ 21-2/077 от 18.05.2021, KGS</t>
         </is>
       </c>
       <c r="B69" s="24" t="n"/>
       <c r="C69" s="24" t="n"/>
-      <c r="D69" s="25" t="n"/>
+      <c r="D69" s="31" t="n">
+        <v>46275</v>
+      </c>
       <c r="E69" s="26" t="n">
-        <v>0</v>
+        <v>1212.15</v>
       </c>
       <c r="F69" s="26" t="n">
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="G69" s="26" t="n">
-        <v>0</v>
+        <v>129.99999</v>
       </c>
       <c r="H69" s="26" t="n">
-        <v>0</v>
+        <v>32.15001</v>
       </c>
       <c r="I69" s="26" t="n">
         <v>0</v>
@@ -5115,22 +5111,22 @@
         <v>0</v>
       </c>
       <c r="U69" s="26" t="n">
-        <v>0</v>
+        <v>1212.15</v>
       </c>
       <c r="V69" s="26" t="n">
-        <v>0</v>
+        <v>404.05</v>
       </c>
       <c r="W69" s="26" t="n">
-        <v>0</v>
+        <v>404.05</v>
       </c>
       <c r="X69" s="26" t="n">
-        <v>0</v>
+        <v>404.05</v>
       </c>
     </row>
     <row r="70" ht="13" customHeight="1">
       <c r="A70" s="14" t="inlineStr">
         <is>
-          <t>Группа 3.1 — процедура банкротства</t>
+          <t>Группа 2.3 — инициирование банкротства</t>
         </is>
       </c>
       <c r="B70" s="15" t="n">
@@ -5204,7 +5200,7 @@
     <row r="71" ht="13" customHeight="1">
       <c r="A71" s="18" t="inlineStr">
         <is>
-          <t>ОсОО «Нарын-Сүт»</t>
+          <t>ОсОО «Талас-Бал»</t>
         </is>
       </c>
       <c r="B71" s="19" t="n"/>
@@ -5276,7 +5272,7 @@
     <row r="72" ht="13" customHeight="1">
       <c r="A72" s="23" t="inlineStr">
         <is>
-          <t>№ 23-5/071 от 09.08.2023, KGS</t>
+          <t>№ 23-4/021 от 21.08.2023, KGS</t>
         </is>
       </c>
       <c r="B72" s="24" t="n"/>
@@ -5346,7 +5342,7 @@
     <row r="73" ht="13" customHeight="1">
       <c r="A73" s="14" t="inlineStr">
         <is>
-          <t>Группа 5 — погашенные</t>
+          <t>Группа 3.1 — процедура банкротства</t>
         </is>
       </c>
       <c r="B73" s="15" t="n">
@@ -5357,19 +5353,19 @@
       </c>
       <c r="D73" s="16" t="n"/>
       <c r="E73" s="17" t="n">
-        <v>840</v>
+        <v>0</v>
       </c>
       <c r="F73" s="17" t="n">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="G73" s="17" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H73" s="17" t="n">
         <v>0</v>
       </c>
       <c r="I73" s="17" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="J73" s="17" t="n">
         <v>0</v>
@@ -5378,10 +5374,10 @@
         <v>0</v>
       </c>
       <c r="L73" s="17" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="M73" s="17" t="n">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="N73" s="17" t="n">
         <v>0</v>
@@ -5390,10 +5386,10 @@
         <v>0</v>
       </c>
       <c r="P73" s="17" t="n">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="Q73" s="17" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="R73" s="17" t="n">
         <v>0</v>
@@ -5402,17 +5398,25 @@
         <v>0</v>
       </c>
       <c r="T73" s="17" t="n">
-        <v>270</v>
-      </c>
-      <c r="U73" s="32" t="n"/>
-      <c r="V73" s="32" t="n"/>
-      <c r="W73" s="32" t="n"/>
-      <c r="X73" s="32" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="U73" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V73" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W73" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X73" s="17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74" ht="13" customHeight="1">
       <c r="A74" s="18" t="inlineStr">
         <is>
-          <t>ОсОО «Ош-Нан»</t>
+          <t>ОсОО «Нарын-Сүт»</t>
         </is>
       </c>
       <c r="B74" s="19" t="n"/>
@@ -5421,19 +5425,19 @@
       </c>
       <c r="D74" s="21" t="n"/>
       <c r="E74" s="22" t="n">
-        <v>840</v>
+        <v>0</v>
       </c>
       <c r="F74" s="22" t="n">
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="G74" s="22" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="H74" s="22" t="n">
         <v>0</v>
       </c>
       <c r="I74" s="22" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="J74" s="22" t="n">
         <v>0</v>
@@ -5442,10 +5446,10 @@
         <v>0</v>
       </c>
       <c r="L74" s="22" t="n">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="M74" s="22" t="n">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="N74" s="22" t="n">
         <v>0</v>
@@ -5454,10 +5458,10 @@
         <v>0</v>
       </c>
       <c r="P74" s="22" t="n">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="Q74" s="22" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="R74" s="22" t="n">
         <v>0</v>
@@ -5466,76 +5470,284 @@
         <v>0</v>
       </c>
       <c r="T74" s="22" t="n">
-        <v>270</v>
-      </c>
-      <c r="U74" s="19" t="n"/>
-      <c r="V74" s="19" t="n"/>
-      <c r="W74" s="19" t="n"/>
-      <c r="X74" s="19" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="U74" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W74" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X74" s="22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75" ht="13" customHeight="1">
       <c r="A75" s="23" t="inlineStr">
         <is>
-          <t>№ 20-1/412 от 14.10.2020, KGS</t>
+          <t>№ 23-5/071 от 09.08.2023, KGS</t>
         </is>
       </c>
       <c r="B75" s="24" t="n"/>
       <c r="C75" s="24" t="n"/>
-      <c r="D75" s="31" t="n">
+      <c r="D75" s="25" t="n"/>
+      <c r="E75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W75" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" ht="13" customHeight="1">
+      <c r="A76" s="14" t="inlineStr">
+        <is>
+          <t>Группа 5.1 — погашенные</t>
+        </is>
+      </c>
+      <c r="B76" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" s="15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D76" s="16" t="n"/>
+      <c r="E76" s="17" t="n">
+        <v>840</v>
+      </c>
+      <c r="F76" s="17" t="n">
+        <v>750</v>
+      </c>
+      <c r="G76" s="17" t="n">
+        <v>90</v>
+      </c>
+      <c r="H76" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="17" t="n">
+        <v>290</v>
+      </c>
+      <c r="J76" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K76" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="17" t="n">
+        <v>290</v>
+      </c>
+      <c r="M76" s="17" t="n">
+        <v>280</v>
+      </c>
+      <c r="N76" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O76" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" s="17" t="n">
+        <v>280</v>
+      </c>
+      <c r="Q76" s="17" t="n">
+        <v>270</v>
+      </c>
+      <c r="R76" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S76" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" s="17" t="n">
+        <v>270</v>
+      </c>
+      <c r="U76" s="32" t="n"/>
+      <c r="V76" s="32" t="n"/>
+      <c r="W76" s="32" t="n"/>
+      <c r="X76" s="32" t="n"/>
+    </row>
+    <row r="77" ht="13" customHeight="1">
+      <c r="A77" s="18" t="inlineStr">
+        <is>
+          <t>ОсОО «Ош-Нан»</t>
+        </is>
+      </c>
+      <c r="B77" s="19" t="n"/>
+      <c r="C77" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D77" s="21" t="n"/>
+      <c r="E77" s="22" t="n">
+        <v>840</v>
+      </c>
+      <c r="F77" s="22" t="n">
+        <v>750</v>
+      </c>
+      <c r="G77" s="22" t="n">
+        <v>90</v>
+      </c>
+      <c r="H77" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="22" t="n">
+        <v>290</v>
+      </c>
+      <c r="J77" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L77" s="22" t="n">
+        <v>290</v>
+      </c>
+      <c r="M77" s="22" t="n">
+        <v>280</v>
+      </c>
+      <c r="N77" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P77" s="22" t="n">
+        <v>280</v>
+      </c>
+      <c r="Q77" s="22" t="n">
+        <v>270</v>
+      </c>
+      <c r="R77" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" s="22" t="n">
+        <v>270</v>
+      </c>
+      <c r="U77" s="19" t="n"/>
+      <c r="V77" s="19" t="n"/>
+      <c r="W77" s="19" t="n"/>
+      <c r="X77" s="19" t="n"/>
+    </row>
+    <row r="78" ht="13" customHeight="1">
+      <c r="A78" s="23" t="inlineStr">
+        <is>
+          <t>№ 20-1/412 от 14.10.2020, KGS</t>
+        </is>
+      </c>
+      <c r="B78" s="24" t="n"/>
+      <c r="C78" s="24" t="n"/>
+      <c r="D78" s="31" t="n">
         <v>46286</v>
       </c>
-      <c r="E75" s="26" t="n">
+      <c r="E78" s="26" t="n">
         <v>840</v>
       </c>
-      <c r="F75" s="26" t="n">
+      <c r="F78" s="26" t="n">
         <v>750</v>
       </c>
-      <c r="G75" s="26" t="n">
+      <c r="G78" s="26" t="n">
         <v>90</v>
       </c>
-      <c r="H75" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="26" t="n">
+      <c r="H78" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="26" t="n">
         <v>290</v>
       </c>
-      <c r="J75" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K75" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="L75" s="26" t="n">
+      <c r="J78" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L78" s="26" t="n">
         <v>290</v>
       </c>
-      <c r="M75" s="26" t="n">
+      <c r="M78" s="26" t="n">
         <v>280</v>
       </c>
-      <c r="N75" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O75" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" s="26" t="n">
+      <c r="N78" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P78" s="26" t="n">
         <v>280</v>
       </c>
-      <c r="Q75" s="26" t="n">
+      <c r="Q78" s="26" t="n">
         <v>270</v>
       </c>
-      <c r="R75" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S75" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T75" s="26" t="n">
+      <c r="R78" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" s="26" t="n">
         <v>270</v>
       </c>
-      <c r="U75" s="24" t="n"/>
-      <c r="V75" s="24" t="n"/>
-      <c r="W75" s="24" t="n"/>
-      <c r="X75" s="24" t="n"/>
+      <c r="U78" s="24" t="n"/>
+      <c r="V78" s="24" t="n"/>
+      <c r="W78" s="24" t="n"/>
+      <c r="X78" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -5728,7 +5940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -5887,7 +6099,7 @@
       </c>
       <c r="B14" s="38" t="inlineStr">
         <is>
-          <t>Строка детали — кредит: план по месяцам года, как он записан в системе на дату «План на». План — вводимая величина «кредит × месяц» в валюте договора; при заведении строка заполняется подсказкой, дальше правится только вручную, и каждая правка хранит, кто, когда и что стояло раньше. Поэтому план на прошлую дату показывается таким, каким он был тогда, а не пересчитывается. В отчёт попадают все кредиты, действовавшие в году (с остатком хотя бы один день года), кроме расторгнутых до выдачи; погашенные и списанные в году — со своим планом до закрытия. Месяц без плана (план не заведён, кредита ещё не было, месяц снят после погашения или списания) — пусто; план, поставленный нулём, — 0,00; кредит без плана на год — строка с пустыми суммами, чтобы пропуск был виден. Колонки: «За год» (всего и по статьям: основная сумма, проценты, штрафы), затем четыре квартала — итог квартала и три месяца одной суммой. Над кредитами разрезы, по умолчанию департамент → группа платёжеспособности → заёмщик; строка кредита («№ … от …, KGS») есть всегда. Заёмщик, подразделение и группа — на дату «План на» (после перевода долга кредит стоит под новым должником, после понижения группы — в новой группе). Первая строка — ИТОГО; строка разреза несёт его итог и стоит над своими строками. Порядок: департаменты — по справочнику оргструктуры; группы — по коду (1.1, 1.2, 2.1 … 5); заёмщики — по алфавиту наименования без организационной формы; кредиты заёмщика — по дате договора. Суммы — в тыс. сом. Кредит в иностранной валюте: все месяцы — по курсу на день, по конец которого учтены правки (по умолчанию — вчера); под кредитом курсивом строка «в тыс. &lt;валюта&gt; (курс …)» с планом в валюте договора, в итоги она не входит. Факта поступлений в отчёте нет — его сравнивает с планом ФО-54. Печать — A3 альбомная в одну страницу по ширине (на A4 масштаб меньше 50 %).</t>
+          <t>Строка детали — кредит: план по месяцам года, как он записан в системе на дату «План на». План — вводимая величина «кредит × месяц» в валюте договора; при заведении строка заполняется подсказкой, дальше правится только вручную, и каждая правка хранит, кто, когда и что стояло раньше. Поэтому план на прошлую дату показывается таким, каким он был тогда, а не пересчитывается. В отчёт попадают все кредиты, действовавшие в году (с остатком хотя бы один день года), кроме расторгнутых до выдачи; погашенные и списанные в году — со своим планом до закрытия. Месяц без плана (план не заведён, кредита ещё не было, месяц снят после погашения или списания) — пусто; план, поставленный нулём, — 0,00; кредит без плана на год — строка с пустыми суммами, чтобы пропуск был виден. Колонки: «За год» (всего и по статьям: основная сумма, проценты, штрафы), затем четыре квартала — итог квартала и три месяца одной суммой. Над кредитами разрезы, по умолчанию департамент → группа платёжеспособности → заёмщик; строка кредита («№ … от …, KGS») есть всегда. Заёмщик, подразделение и группа — на дату «План на» (после перевода долга кредит стоит под новым должником, после понижения группы — в новой группе). Первая строка — ИТОГО; строка разреза несёт его итог и стоит над своими строками. Порядок: департаменты — по справочнику оргструктуры; группы — по коду (1.1, 1.2, 2.1 … 5.1, 5.2); заёмщики — по алфавиту наименования без организационной формы; кредиты заёмщика — по дате договора. Суммы — в тыс. сом. Кредит в иностранной валюте: все месяцы — по курсу на день, по конец которого учтены правки (по умолчанию — вчера); под кредитом курсивом строка «в тыс. &lt;валюта&gt; (курс …)» с планом в валюте договора, в итоги она не входит. Факта поступлений в отчёте нет — его сравнивает с планом ФО-54. Печать — A3 альбомная в одну страницу по ширине (на A4 масштаб меньше 50 %).</t>
         </is>
       </c>
     </row>
@@ -6370,7 +6582,7 @@
       </c>
       <c r="B48" s="38" t="inlineStr">
         <is>
-          <t>2026 год, план на 01.10.2026: заёмщиков 23, кредитов 26; за год 26 516,816 тыс. сом, в том числе основная сумма 22 121,738, проценты 4 344,528, штрафы 50,550; кварталы 6 903,226 · 7 299,326 · 6 052,045 · 6 262,220.</t>
+          <t>2026 год, план на 01.10.2026: заёмщиков 24, кредитов 27; за год 28 203,828 тыс. сом, в том числе основная сумма 23 339,738, проценты 4 813,540, штрафы 50,550; кварталы 8 250,821 · 7 412,876 · 6 165,595 · 6 374,536.</t>
         </is>
       </c>
     </row>
@@ -6386,7 +6598,7 @@
         </is>
       </c>
     </row>
-    <row r="50" ht="45" customHeight="1">
+    <row r="50" ht="60" customHeight="1">
       <c r="A50" s="37" t="inlineStr">
         <is>
           <t>3.</t>
@@ -6394,7 +6606,7 @@
       </c>
       <c r="B50" s="38" t="inlineStr">
         <is>
-          <t>План месяца по кредиту — тот, что записан в системе на дату «План на» (карточка кредита, вкладка «План и исполнение»); план сентября по кредиту = «По плану за период» ФО-54 за сентябрь 2026. КЗ-01: октябрь 169,271 по № 21-3/117 и 111,458 по № 22-2/031 — как платежи октября в ФО-05.</t>
+          <t>План месяца по кредиту — тот, что записан в системе на дату «План на» (карточка кредита, вкладка «План и исполнение»); план сентября по кредиту = «По плану за период» ФО-54 за сентябрь 2026 (ИТОГО сентября 1 962,365, с КЗ-25 38,261). КЗ-01: октябрь 169,271 по № 21-3/117 и 111,458 по № 22-2/031 — как платежи октября в ФО-05.</t>
         </is>
       </c>
     </row>
@@ -6442,11 +6654,11 @@
       </c>
       <c r="B54" s="38" t="inlineStr">
         <is>
-          <t>Валютные КЗ-11, КЗ-21 № 19-3/061, КЗ-23 (USD 87,50000) и КЗ-22 (EUR 101,50000): все месяцы по курсу на 30.09.2026; КЗ-11 за год 5 604,375 тыс. сом = 64,050 тыс. USD × 87,50000, строка «в тыс. USD (курс 87,50000)» под кредитом.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="45" customHeight="1">
+          <t>Валютные КЗ-11, КЗ-21 № 19-3/061, КЗ-23 (USD 87,50000) и КЗ-22, КЗ-25 (EUR 101,50000): все месяцы по курсу на 30.09.2026; КЗ-11 за год 5 604,375 тыс. сом = 64,050 тыс. USD × 87,50000, строка «в тыс. USD (курс 87,50000)» под кредитом.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="105" customHeight="1">
       <c r="A55" s="37" t="inlineStr">
         <is>
           <t>8.</t>
@@ -6454,17 +6666,30 @@
       </c>
       <c r="B55" s="38" t="inlineStr">
         <is>
-          <t>КЗ-07 — под заёмщиком ОсОО «Ысык-Көл Логистик» (долг переведён 09.09.2026), группа 1.1; КЗ-19 — в группе 3.1 (понижена 22.09.2026); КЗ-21 — одна строка заёмщика, три кредита по дате договора. Не показан КЗ-18 (расторгнут до выдачи).</t>
+          <t>КЗ-25 № 21-9/040 (EUR, Департамент администрирования кредитов, группа 1.1, «Ала-Арча Энерго» после «Ак-Дан»): план по графику набора — проценты ежемесячно за 21-е – 20-е число, факт/360, основная сумма 12 000,00 EUR 20.03.2026 (до неё остаток 84 000,00, после — 72 000,00 EUR); за год 16,62081 тыс. EUR = 1 687,011 тыс. сом (основная сумма 1 218,000, проценты 469,011); март 1 258,319; сентябрь 376,96 EUR = 38,261 (= ФО-54, ФО-05 «Оплачено» — по курсу 30.09.2026, ФО-04 по курсу дня платежа — 38,167); октябрь 364,80 EUR = 37,027 (= ФО-05); январь–сентябрь 15 514,24 EUR — как «С начала года» ФО-04|Собрано за месяц; «План изменён» пусто.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="75" customHeight="1">
+      <c r="A56" s="37" t="inlineStr">
+        <is>
+          <t>9.</t>
+        </is>
+      </c>
+      <c r="B56" s="38" t="inlineStr">
+        <is>
+          <t>КЗ-07 — под заёмщиком ОсОО «Ысык-Көл Логистик» (долг переведён 09.09.2026), группа 1.1; группы — на 01.10.2026: КЗ-05 — 2.2, КЗ-23 — 2.1, КЗ-19 — 3.1 (понижена 22.09.2026), КЗ-15 и КЗ-16 — 5.1 «погашенные», КЗ-08 — 5.2 «списанные» (с 17.09.2026); в группе 4 на дату никого нет; КЗ-21 — одна строка заёмщика, три кредита по дате договора. Не показаны КЗ-18 (расторгнут до выдачи) и КЗ-26 (не освоен — остатка в году не было).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="25">
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B54:C54"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B56:C56"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="B52:C52"/>
     <mergeCell ref="B48:C48"/>
